--- a/2026/08/22/uranium-companies-comparison/uranium-three-company-comparison-model-2026-2035.xlsx
+++ b/2026/08/22/uranium-companies-comparison/uranium-three-company-comparison-model-2026-2035.xlsx
@@ -2,27 +2,33 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公司画像" sheetId="1" r:id="R362fee4815fa4ac7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统一Common" sheetId="2" r:id="Rb80f3fe00a0b4c61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史财务" sheetId="3" r:id="Re372e05262d24753"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务历史" sheetId="4" r:id="Reb778eb4e99f4483"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测总表" sheetId="5" r:id="Rae52021404744536"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务预测" sheetId="6" r:id="R7d56de3044b1470b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="估值明细" sheetId="7" r:id="Reb4c3d2b52754a24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐年股价" sheetId="8" r:id="R2f1401f6de0945f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资本配置" sheetId="9" r:id="R80fe7a6b81fd4e7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计记录" sheetId="10" r:id="Rc5befb03a4724fd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="11" r:id="R0b92e8a22a7348af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="12" r:id="R332d9ce01f724e6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="监控证伪" sheetId="13" r:id="R8a7514149e794def"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="14" r:id="Rbe92be99b41e45a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史对照_补充" sheetId="15" r:id="Rcc2e9caf9b874b1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四情景预测_补充" sheetId="16" r:id="Rfd28de7e14004847"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务增速_补充" sheetId="17" r:id="R5b2e136aacb04413"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四情景估值_补充" sheetId="18" r:id="Rc539fff42bf9416b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中核国际SB计算" sheetId="19" r:id="Rb017a56d8e8f404c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充审计" sheetId="20" r:id="Rb9b76af52b164d51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="估值步骤" sheetId="21" r:id="R6e80302aab02412f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公司画像" sheetId="1" r:id="Rcdca02ef1c2240e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统一Common" sheetId="2" r:id="R86e1b50ae9f4496e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史财务" sheetId="3" r:id="R218d25bfbec24008"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务历史" sheetId="4" r:id="Re011942dcfef4d07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="预测总表" sheetId="5" r:id="R1942ca9cde13400e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务预测" sheetId="6" r:id="Rc37c4f692ec04ae4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="估值明细" sheetId="7" r:id="Rccc89a9792f942da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐年股价" sheetId="8" r:id="R94cb12ff737041b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资本配置" sheetId="9" r:id="Rb48bb34c90ff4176"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="审计记录" sheetId="10" r:id="Re7afba1b483e45cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="11" r:id="R52517f9dcaef4ab9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="12" r:id="R9b8ca6862ed54cd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="监控证伪" sheetId="13" r:id="Rd78aea80680242a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="14" r:id="Ra07f2484736445d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史对照_补充" sheetId="15" r:id="Rfd8f48d4390b4904"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四情景预测_补充" sheetId="16" r:id="Rfb59ba536b2946d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="业务增速_补充" sheetId="17" r:id="R4ccf501f80fc474c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四情景估值_补充" sheetId="18" r:id="R8dec7130e4134403"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中核国际SB计算" sheetId="19" r:id="Rca85e8532cee4c9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补充审计" sheetId="20" r:id="Re103cf34c45841c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="估值步骤" sheetId="21" r:id="R35971452c1474ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026H1财报更新" sheetId="22" r:id="Rd795362362c94652"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新后预测" sheetId="23" r:id="R1e96ca3f66394629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新后估值" sheetId="24" r:id="Re8ef32216f8141c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="股价历史与合理价" sheetId="25" r:id="Rd0b6401d84ca4c04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新记录" sheetId="26" r:id="R57c05a48df80403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新检查" sheetId="27" r:id="Rf11625a95bf64239"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -33,7 +39,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="13">
+  <x:numFmts count="16">
     <x:numFmt numFmtId="200" formatCode="0.00;[Red](0.00);-"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.0;[Red](#,##0.0);-"/>
     <x:numFmt numFmtId="202" formatCode="0"/>
@@ -47,8 +53,11 @@
     <x:numFmt numFmtId="210" formatCode="#,##0.00;[Red]-#,##0.00"/>
     <x:numFmt numFmtId="211" formatCode="0.000;[Red]-0.000"/>
     <x:numFmt numFmtId="212" formatCode="0.00x"/>
+    <x:numFmt numFmtId="213" formatCode="#,##0.000"/>
+    <x:numFmt numFmtId="214" formatCode="#,##0"/>
+    <x:numFmt numFmtId="215" formatCode="#,##0.0"/>
   </x:numFmts>
-  <x:fonts count="16">
+  <x:fonts count="19">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -137,8 +146,25 @@
       <x:color rgb="FF222222"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF9C0006"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF44546A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="19">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -210,8 +236,28 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="4">
     <x:border/>
     <x:border/>
     <x:border>
@@ -228,11 +274,25 @@
         <x:color rgb="FFD9E1F2"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="161">
+  <x:cellXfs count="192">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -596,11 +656,90 @@
     <x:xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="214" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="215" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="214" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="0" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="2">
+  <x:dxfs count="6">
     <x:dxf>
       <x:font>
         <x:color rgb="FF006100"/>
@@ -618,6 +757,49 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -982,6 +1164,726 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/drawings/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:t>中国铀业：历史收盘价—未来四情景合理价</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>历史收盘价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$5:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$B$5:$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Bear合理价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$5:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$C$5:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Base合理价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$5:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$D$5:$D$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Bull合理价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$5:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$E$5:$E$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>Super Bull合理价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$5:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$F$5:$F$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:smooth val="0"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="675"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:t>中广核矿业：历史收盘价—未来四情景合理价</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>历史收盘价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$20:$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$B$20:$B$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Bear合理价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$20:$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$C$20:$C$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Base合理价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$20:$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$D$20:$D$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Bull合理价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$20:$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$E$20:$E$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>Super Bull合理价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$20:$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$F$20:$F$30</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:smooth val="0"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="675"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:t>中核国际：历史收盘价—未来四情景合理价</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>历史收盘价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$35:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$B$35:$B$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Bear合理价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$35:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$C$35:$C$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Base合理价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$35:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$D$35:$D$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Bull合理价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$35:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$E$35:$E$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>Super Bull合理价</c:v>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'股价历史与合理价'!$A$35:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'股价历史与合理价'!$F$35:$F$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:smooth val="0"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="675"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor>
@@ -1008,7 +1910,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8314f4beff224226"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R719bf5f9fdf440b6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1038,7 +1940,102 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9af0d212436e4ed0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4c69bd0e806c4d15"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf340b23eee8f4be0"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc06c055fede34779"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rda2850f469d444a1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1349,16 +2346,17 @@
         <x:v>RMB</x:v>
       </x:c>
       <x:c r="D4" s="32" t="n">
-        <x:v>67.03</x:v>
+        <x:v>66.42</x:v>
       </x:c>
       <x:c r="E4" s="32" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="F4" s="28" t="n">
         <x:v>2068.181818</x:v>
       </x:c>
       <x:c r="G4" s="36" t="n">
-        <x:v>138630.22726054</x:v>
+        <x:f>D4*F4</x:f>
+        <x:v>137368.63635156</x:v>
       </x:c>
       <x:c r="H4" s="28" t="str">
         <x:v>A+C+D</x:v>
@@ -1379,7 +2377,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="N4" s="28" t="str">
-        <x:v>研究包+Step6；2026Q1锚点已在原包中</x:v>
+        <x:v>2026H1中报+2026-09-02未复权收盘价；详见新增更新表</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1393,16 +2391,17 @@
         <x:v>HKD</x:v>
       </x:c>
       <x:c r="D5" s="32" t="n">
-        <x:v>2.97</x:v>
+        <x:v>2.43</x:v>
       </x:c>
       <x:c r="E5" s="32" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="F5" s="28" t="n">
         <x:v>7600.682645</x:v>
       </x:c>
       <x:c r="G5" s="36" t="n">
-        <x:v>22574.02745565</x:v>
+        <x:f>D5*F5</x:f>
+        <x:v>18469.658827350002</x:v>
       </x:c>
       <x:c r="H5" s="28" t="str">
         <x:v>B+C</x:v>
@@ -1423,7 +2422,7 @@
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="N5" s="28" t="str">
-        <x:v>研究包+Step6；2026Q2矿山运营锚点已纳入原包</x:v>
+        <x:v>2026H1中报+2026-09-02未复权收盘价；详见新增更新表</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1437,16 +2436,17 @@
         <x:v>HKD</x:v>
       </x:c>
       <x:c r="D6" s="32" t="n">
-        <x:v>4.3</x:v>
+        <x:v>3.85</x:v>
       </x:c>
       <x:c r="E6" s="32" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="F6" s="28" t="n">
         <x:v>489.168308</x:v>
       </x:c>
       <x:c r="G6" s="36" t="n">
-        <x:v>2103.4237244</x:v>
+        <x:f>D6*F6</x:f>
+        <x:v>1883.2979858</x:v>
       </x:c>
       <x:c r="H6" s="28" t="str">
         <x:v>C+D</x:v>
@@ -1467,7 +2467,7 @@
         <x:v>Medium-Low for 2026 / Medium long term</x:v>
       </x:c>
       <x:c r="N6" s="28" t="str">
-        <x:v>研究包；2026-08-05 HKEX profit alert作为外部审计更新</x:v>
+        <x:v>2026H1中报+2026-09-02未复权收盘价；详见新增更新表</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3416,6 +4416,230 @@
         <x:v>Public web search at audit date did not return a clean 2026-08-21 row; retain source-package anchor and flag.</x:v>
       </x:c>
     </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B38" s="176" t="str">
+        <x:v>WEB_H1_20260829</x:v>
+      </x:c>
+      <x:c r="C38" s="176" t="str">
+        <x:v>interim</x:v>
+      </x:c>
+      <x:c r="D38" s="176" t="str">
+        <x:v>2026年半年度报告</x:v>
+      </x:c>
+      <x:c r="E38" s="176" t="str">
+        <x:v>中国铀业股份有限公司</x:v>
+      </x:c>
+      <x:c r="F38" s="176" t="str">
+        <x:v>2026-08-29</x:v>
+      </x:c>
+      <x:c r="G38" s="176" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-08-29/1225527801.PDF</x:v>
+      </x:c>
+      <x:c r="H38" s="176" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I38" s="176" t="str">
+        <x:v>H1财务、分产品收入与毛利、营运资金</x:v>
+      </x:c>
+      <x:c r="J38" s="176" t="str">
+        <x:v>本次模型更新的最新官方来源</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B39" s="176" t="str">
+        <x:v>WEB_H1_20260827</x:v>
+      </x:c>
+      <x:c r="C39" s="176" t="str">
+        <x:v>interim</x:v>
+      </x:c>
+      <x:c r="D39" s="176" t="str">
+        <x:v>Interim Results 2026</x:v>
+      </x:c>
+      <x:c r="E39" s="176" t="str">
+        <x:v>CGN Mining Company Limited</x:v>
+      </x:c>
+      <x:c r="F39" s="176" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="G39" s="176" t="str">
+        <x:v>https://www1.hkexnews.hk/listedco/listconews/sehk/2026/0827/2026082702321.pdf</x:v>
+      </x:c>
+      <x:c r="H39" s="176" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I39" s="176" t="str">
+        <x:v>H1财务、权益产量、矿山成本、贸易与交付</x:v>
+      </x:c>
+      <x:c r="J39" s="176" t="str">
+        <x:v>本次模型更新的最新官方来源</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B40" s="176" t="str">
+        <x:v>WEB_H1_20260826</x:v>
+      </x:c>
+      <x:c r="C40" s="176" t="str">
+        <x:v>interim</x:v>
+      </x:c>
+      <x:c r="D40" s="176" t="str">
+        <x:v>Interim Results 2026</x:v>
+      </x:c>
+      <x:c r="E40" s="176" t="str">
+        <x:v>CNNC International Limited</x:v>
+      </x:c>
+      <x:c r="F40" s="176" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="G40" s="176" t="str">
+        <x:v>https://www1.hkexnews.hk/listedco/listconews/sehk/2026/0826/2026082601623.pdf</x:v>
+      </x:c>
+      <x:c r="H40" s="176" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I40" s="176" t="str">
+        <x:v>H1财务、交易量、关联交易框架、现金</x:v>
+      </x:c>
+      <x:c r="J40" s="176" t="str">
+        <x:v>本次模型更新的最新官方来源</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B41" s="176" t="str">
+        <x:v>WEB_PRICE_20260902</x:v>
+      </x:c>
+      <x:c r="C41" s="176" t="str">
+        <x:v>market_price</x:v>
+      </x:c>
+      <x:c r="D41" s="176" t="str">
+        <x:v>001280.SZ Historical Data</x:v>
+      </x:c>
+      <x:c r="E41" s="176" t="str">
+        <x:v>Yahoo Finance</x:v>
+      </x:c>
+      <x:c r="F41" s="176" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="G41" s="176" t="str">
+        <x:v>https://finance.yahoo.com/quote/001280.SZ/history/</x:v>
+      </x:c>
+      <x:c r="H41" s="176" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I41" s="176" t="str">
+        <x:v>2025年末与2026-09-02未复权收盘价</x:v>
+      </x:c>
+      <x:c r="J41" s="176" t="str">
+        <x:v>图表历史价格口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B42" s="176" t="str">
+        <x:v>WEB_PRICE_20260902</x:v>
+      </x:c>
+      <x:c r="C42" s="176" t="str">
+        <x:v>market_price</x:v>
+      </x:c>
+      <x:c r="D42" s="176" t="str">
+        <x:v>1164.HK Historical Data</x:v>
+      </x:c>
+      <x:c r="E42" s="176" t="str">
+        <x:v>Yahoo Finance</x:v>
+      </x:c>
+      <x:c r="F42" s="176" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="G42" s="176" t="str">
+        <x:v>https://finance.yahoo.com/quote/1164.HK/history/</x:v>
+      </x:c>
+      <x:c r="H42" s="176" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I42" s="176" t="str">
+        <x:v>2021—2025年末与2026-09-02未复权收盘价</x:v>
+      </x:c>
+      <x:c r="J42" s="176" t="str">
+        <x:v>图表历史价格口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B43" s="176" t="str">
+        <x:v>WEB_PRICE_20260902</x:v>
+      </x:c>
+      <x:c r="C43" s="176" t="str">
+        <x:v>market_price</x:v>
+      </x:c>
+      <x:c r="D43" s="176" t="str">
+        <x:v>2302.HK Historical Data</x:v>
+      </x:c>
+      <x:c r="E43" s="176" t="str">
+        <x:v>Yahoo Finance</x:v>
+      </x:c>
+      <x:c r="F43" s="176" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="G43" s="176" t="str">
+        <x:v>https://finance.yahoo.com/quote/2302.HK/history/</x:v>
+      </x:c>
+      <x:c r="H43" s="176" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I43" s="176" t="str">
+        <x:v>2021—2025年末与2026-09-02未复权收盘价</x:v>
+      </x:c>
+      <x:c r="J43" s="176" t="str">
+        <x:v>图表历史价格口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="176" t="str">
+        <x:v>公共</x:v>
+      </x:c>
+      <x:c r="B44" s="176" t="str">
+        <x:v>MODEL_UPDATE_20260902</x:v>
+      </x:c>
+      <x:c r="C44" s="176" t="str">
+        <x:v>model_change</x:v>
+      </x:c>
+      <x:c r="D44" s="176" t="str">
+        <x:v>2026H1财报更新说明</x:v>
+      </x:c>
+      <x:c r="E44" s="176" t="str">
+        <x:v>本工作簿</x:v>
+      </x:c>
+      <x:c r="F44" s="176" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="G44" s="176" t="str">
+        <x:v>更新记录</x:v>
+      </x:c>
+      <x:c r="H44" s="176" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I44" s="176" t="str">
+        <x:v>旧模型到新模型的桥接</x:v>
+      </x:c>
+      <x:c r="J44" s="176" t="str">
+        <x:v>保留旧表，不静默覆盖</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
@@ -3846,7 +5070,7 @@
         <x:v>估值日</x:v>
       </x:c>
       <x:c r="B5" s="92" t="str">
-        <x:v>2026-08-21</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="C5" s="92" t="str">
         <x:v>要求回报率</x:v>
@@ -3964,31 +5188,27 @@
         <x:v>中国铀业</x:v>
       </x:c>
       <x:c r="B9" s="105" t="n">
-        <x:f>'公司画像'!D4</x:f>
-        <x:v>67.03</x:v>
+        <x:v>66.42</x:v>
       </x:c>
       <x:c r="C9" s="105" t="n">
-        <x:f>'逐年股价'!F8</x:f>
-        <x:v>4.913076</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="D9" s="105" t="n">
-        <x:f>'逐年股价'!F15</x:f>
-        <x:v>21.623061</x:v>
+        <x:v>21.6</x:v>
       </x:c>
       <x:c r="E9" s="105" t="n">
-        <x:f>'逐年股价'!F22</x:f>
-        <x:v>30.823777</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F9" s="106" t="n">
-        <x:f>'逐年股价'!J15</x:f>
-        <x:v>-0.22125915737437557</x:v>
+        <x:f>'更新后估值'!G6</x:f>
+        <x:v>-0.21858081687046116</x:v>
       </x:c>
       <x:c r="G9" s="105" t="n">
-        <x:f>'逐年股价'!K15</x:f>
-        <x:v>14.6252270978498</x:v>
+        <x:f>'更新后估值'!I6</x:f>
+        <x:v>14.693685065360688</x:v>
       </x:c>
       <x:c r="H9" s="92" t="str">
-        <x:v>资产/增长质量强，但现价显著透支标准Base</x:v>
+        <x:v>最新中报后仍无标准情景通过11%</x:v>
       </x:c>
       <x:c r="I9" s="92"/>
       <x:c r="J9" s="92"/>
@@ -4005,31 +5225,27 @@
         <x:v>中广核矿业</x:v>
       </x:c>
       <x:c r="B10" s="105" t="n">
-        <x:f>'公司画像'!D5</x:f>
-        <x:v>2.97</x:v>
+        <x:v>2.43</x:v>
       </x:c>
       <x:c r="C10" s="105" t="n">
-        <x:f>'逐年股价'!F29</x:f>
-        <x:v>0.5387145857492853</x:v>
+        <x:v>0.446</x:v>
       </x:c>
       <x:c r="D10" s="105" t="n">
-        <x:f>'逐年股价'!F39</x:f>
-        <x:v>1.0094629056590525</x:v>
+        <x:v>0.874</x:v>
       </x:c>
       <x:c r="E10" s="105" t="n">
-        <x:f>'逐年股价'!F49</x:f>
-        <x:v>1.4891650180439802</x:v>
+        <x:v>1.271</x:v>
       </x:c>
       <x:c r="F10" s="106" t="n">
-        <x:f>'逐年股价'!J39</x:f>
-        <x:v>-0.19740850279520833</x:v>
+        <x:f>'更新后估值'!G10</x:f>
+        <x:v>-0.1746834805982519</x:v>
       </x:c>
       <x:c r="G10" s="105" t="n">
-        <x:f>'逐年股价'!K39</x:f>
-        <x:v>0.7830469639132949</x:v>
+        <x:f>'更新后估值'!I10</x:f>
+        <x:v>0.6981225086330841</x:v>
       </x:c>
       <x:c r="H10" s="92" t="str">
-        <x:v>底层矿山质量好，但现价已含较强铀价预期</x:v>
+        <x:v>成本上修后仍仅Super Bull通过11%</x:v>
       </x:c>
       <x:c r="I10" s="92"/>
       <x:c r="J10" s="92"/>
@@ -4046,31 +5262,27 @@
         <x:v>中核国际</x:v>
       </x:c>
       <x:c r="B11" s="105" t="n">
-        <x:f>'公司画像'!D6</x:f>
-        <x:v>4.3</x:v>
+        <x:v>3.85</x:v>
       </x:c>
       <x:c r="C11" s="105" t="n">
-        <x:f>'逐年股价'!F59</x:f>
-        <x:v>2.1376</x:v>
+        <x:v>1.881</x:v>
       </x:c>
       <x:c r="D11" s="105" t="n">
-        <x:f>'逐年股价'!F69</x:f>
-        <x:v>5.8768</x:v>
+        <x:v>5.429</x:v>
       </x:c>
       <x:c r="E11" s="105" t="n">
-        <x:f>'逐年股价'!F79</x:f>
-        <x:v>7.5576</x:v>
+        <x:v>7.069</x:v>
       </x:c>
       <x:c r="F11" s="106" t="n">
-        <x:f>'逐年股价'!J69</x:f>
-        <x:v>0.07425546901687963</x:v>
+        <x:f>'更新后估值'!G14</x:f>
+        <x:v>0.08264016899666315</x:v>
       </x:c>
       <x:c r="G11" s="105" t="n">
-        <x:f>'逐年股价'!K69</x:f>
-        <x:v>3.7279445059630123</x:v>
+        <x:f>'更新后估值'!I14</x:f>
+        <x:v>3.4556404010593846</x:v>
       </x:c>
       <x:c r="H11" s="92" t="str">
-        <x:v>现金垫最好；Base仍低于11%，Bull可越过门槛</x:v>
+        <x:v>Base约8%，Bull与Super Bull通过11%</x:v>
       </x:c>
       <x:c r="I11" s="92"/>
       <x:c r="J11" s="92"/>
@@ -4157,16 +5369,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C15" s="107" t="n">
-        <x:f>C9/B9</x:f>
-        <x:v>0.07329667313143369</x:v>
+        <x:v>0.07828967178560675</x:v>
       </x:c>
       <x:c r="D15" s="107" t="n">
-        <x:f>D9/B9</x:f>
-        <x:v>0.3225878114277189</x:v>
+        <x:v>0.3252032520325203</x:v>
       </x:c>
       <x:c r="E15" s="107" t="n">
-        <x:f>E9/B9</x:f>
-        <x:v>0.45985046993883333</x:v>
+        <x:v>0.45167118337850043</x:v>
       </x:c>
       <x:c r="F15" s="92"/>
       <x:c r="G15" s="92"/>
@@ -4189,16 +5398,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C16" s="107" t="n">
-        <x:f>C10/B10</x:f>
-        <x:v>0.18138538240716676</x:v>
+        <x:v>0.18339605034684842</x:v>
       </x:c>
       <x:c r="D16" s="107" t="n">
-        <x:f>D10/B10</x:f>
-        <x:v>0.3398865002219032</x:v>
+        <x:v>0.3597585470228848</x:v>
       </x:c>
       <x:c r="E16" s="107" t="n">
-        <x:f>E10/B10</x:f>
-        <x:v>0.5014023629777711</x:v>
+        <x:v>0.5231967998575013</x:v>
       </x:c>
       <x:c r="F16" s="92"/>
       <x:c r="G16" s="92"/>
@@ -4221,16 +5427,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C17" s="107" t="n">
-        <x:f>C11/B11</x:f>
-        <x:v>0.49711627906976746</x:v>
+        <x:v>0.48863827399522725</x:v>
       </x:c>
       <x:c r="D17" s="107" t="n">
-        <x:f>D11/B11</x:f>
-        <x:v>1.3666976744186048</x:v>
+        <x:v>1.41031560540418</x:v>
       </x:c>
       <x:c r="E17" s="107" t="n">
-        <x:f>E11/B11</x:f>
-        <x:v>1.7575813953488373</x:v>
+        <x:v>1.836185863773996</x:v>
       </x:c>
       <x:c r="F17" s="92"/>
       <x:c r="G17" s="92"/>
@@ -4642,14 +5845,16 @@
       <x:c r="Q31" s="92"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="92"/>
-      <x:c r="B32" s="92"/>
-      <x:c r="C32" s="92"/>
-      <x:c r="D32" s="92"/>
-      <x:c r="E32" s="92"/>
-      <x:c r="F32" s="92"/>
-      <x:c r="G32" s="92"/>
-      <x:c r="H32" s="92"/>
+      <x:c r="A32" s="162" t="str">
+        <x:v>版本提示：第1—30行为2026-09-02更新后的摘要；完整公式以“更新后预测”“更新后估值”“股价历史与合理价”为准，旧表保留用于变更追溯。</x:v>
+      </x:c>
+      <x:c r="B32" s="162"/>
+      <x:c r="C32" s="162"/>
+      <x:c r="D32" s="162"/>
+      <x:c r="E32" s="162"/>
+      <x:c r="F32" s="162"/>
+      <x:c r="G32" s="162"/>
+      <x:c r="H32" s="162"/>
       <x:c r="I32" s="92"/>
       <x:c r="J32" s="92"/>
       <x:c r="K32" s="92"/>
@@ -4690,6 +5895,7 @@
     <x:mergeCell ref="F25:H26"/>
     <x:mergeCell ref="F27:H28"/>
     <x:mergeCell ref="F29:H30"/>
+    <x:mergeCell ref="A32:H32"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="F9:F11">
     <x:cfRule type="expression" dxfId="0" priority="1">
@@ -4700,7 +5906,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19603a74b1ea4900"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99f30247f6254528"/>
 </x:worksheet>
 </file>
 
@@ -19828,6 +21034,5892 @@
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="38" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="52" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="165" t="str">
+        <x:v>2026H1 最新财报更新</x:v>
+      </x:c>
+      <x:c r="B1" s="165"/>
+      <x:c r="C1" s="165"/>
+      <x:c r="D1" s="165"/>
+      <x:c r="E1" s="165"/>
+      <x:c r="F1" s="165"/>
+      <x:c r="G1" s="165"/>
+      <x:c r="H1" s="165"/>
+      <x:c r="I1" s="165"/>
+      <x:c r="J1" s="165"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="169" t="str">
+        <x:v>金额单位均为百万本币；中国铀业为人民币，中广核矿业和中核国际为港币。蓝色字体为外部输入，黑色公式为计算，绿色为经财报核对的结果。数据截止2026-09-02。</x:v>
+      </x:c>
+      <x:c r="B2" s="169"/>
+      <x:c r="C2" s="169"/>
+      <x:c r="D2" s="169"/>
+      <x:c r="E2" s="169"/>
+      <x:c r="F2" s="169"/>
+      <x:c r="G2" s="169"/>
+      <x:c r="H2" s="169"/>
+      <x:c r="I2" s="169"/>
+      <x:c r="J2" s="169"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="174" t="str">
+        <x:v>公司</x:v>
+      </x:c>
+      <x:c r="B4" s="174" t="str">
+        <x:v>指标</x:v>
+      </x:c>
+      <x:c r="C4" s="174" t="str">
+        <x:v>2026H1</x:v>
+      </x:c>
+      <x:c r="D4" s="174" t="str">
+        <x:v>2025H1</x:v>
+      </x:c>
+      <x:c r="E4" s="174" t="str">
+        <x:v>同比/变化</x:v>
+      </x:c>
+      <x:c r="F4" s="174" t="str">
+        <x:v>单位</x:v>
+      </x:c>
+      <x:c r="G4" s="174" t="str">
+        <x:v>模型含义</x:v>
+      </x:c>
+      <x:c r="H4" s="174" t="str">
+        <x:v>来源日期</x:v>
+      </x:c>
+      <x:c r="I4" s="174" t="str">
+        <x:v>官方来源</x:v>
+      </x:c>
+      <x:c r="J4" s="174" t="str">
+        <x:v>审计备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="180" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B5" s="176" t="str">
+        <x:v>营业收入</x:v>
+      </x:c>
+      <x:c r="C5" s="178" t="n">
+        <x:v>10582.881</x:v>
+      </x:c>
+      <x:c r="D5" s="178" t="n">
+        <x:v>9551.334</x:v>
+      </x:c>
+      <x:c r="E5" s="179" t="n">
+        <x:f>IFERROR(C5/D5-1,"")</x:f>
+        <x:v>0.10800030655403714</x:v>
+      </x:c>
+      <x:c r="F5" s="176" t="str">
+        <x:v>RMB m</x:v>
+      </x:c>
+      <x:c r="G5" s="181" t="str">
+        <x:v>总收入仍增长；自产铀收入下降被外购、稀土副产品等抵消</x:v>
+      </x:c>
+      <x:c r="H5" s="181" t="str">
+        <x:v>2026-08-29</x:v>
+      </x:c>
+      <x:c r="I5" s="181" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-08-29/1225527801.PDF</x:v>
+      </x:c>
+      <x:c r="J5" s="181" t="str">
+        <x:v>财报原值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="180" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B6" s="176" t="str">
+        <x:v>归母净利润</x:v>
+      </x:c>
+      <x:c r="C6" s="178" t="n">
+        <x:v>987.424</x:v>
+      </x:c>
+      <x:c r="D6" s="178" t="n">
+        <x:v>764.993</x:v>
+      </x:c>
+      <x:c r="E6" s="179" t="n">
+        <x:f>IFERROR(C6/D6-1,"")</x:f>
+        <x:v>0.29076213769276316</x:v>
+      </x:c>
+      <x:c r="F6" s="176" t="str">
+        <x:v>RMB m</x:v>
+      </x:c>
+      <x:c r="G6" s="181" t="str">
+        <x:v>近端盈利好于旧模型的担忧，但不等于估值倍数可以维持</x:v>
+      </x:c>
+      <x:c r="H6" s="181" t="str">
+        <x:v>2026-08-29</x:v>
+      </x:c>
+      <x:c r="I6" s="181" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-08-29/1225527801.PDF</x:v>
+      </x:c>
+      <x:c r="J6" s="181" t="str">
+        <x:v>财报原值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="180" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B7" s="176" t="str">
+        <x:v>经营现金流</x:v>
+      </x:c>
+      <x:c r="C7" s="178" t="n">
+        <x:v>349.001</x:v>
+      </x:c>
+      <x:c r="D7" s="178" t="n">
+        <x:v>-3885.735</x:v>
+      </x:c>
+      <x:c r="E7" s="179" t="n">
+        <x:f>IFERROR(C7/D7-1,"")</x:f>
+        <x:v>-1.0898159550252398</x:v>
+      </x:c>
+      <x:c r="F7" s="176" t="str">
+        <x:v>RMB m</x:v>
+      </x:c>
+      <x:c r="G7" s="181" t="str">
+        <x:v>现金流转正；库存下降但应收大增，风险由库存转向回款</x:v>
+      </x:c>
+      <x:c r="H7" s="181" t="str">
+        <x:v>2026-08-29</x:v>
+      </x:c>
+      <x:c r="I7" s="181" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-08-29/1225527801.PDF</x:v>
+      </x:c>
+      <x:c r="J7" s="181" t="str">
+        <x:v>财报原值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="180" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B8" s="176" t="str">
+        <x:v>存货</x:v>
+      </x:c>
+      <x:c r="C8" s="178" t="n">
+        <x:v>10541.623</x:v>
+      </x:c>
+      <x:c r="D8" s="178" t="n">
+        <x:v>11674.385</x:v>
+      </x:c>
+      <x:c r="E8" s="179" t="n">
+        <x:f>IFERROR(C8/D8-1,"")</x:f>
+        <x:v>-0.09702969364124969</x:v>
+      </x:c>
+      <x:c r="F8" s="176" t="str">
+        <x:v>RMB m</x:v>
+      </x:c>
+      <x:c r="G8" s="181" t="str">
+        <x:v>较2025年末下降</x:v>
+      </x:c>
+      <x:c r="H8" s="181" t="str">
+        <x:v>2026-08-29</x:v>
+      </x:c>
+      <x:c r="I8" s="181" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-08-29/1225527801.PDF</x:v>
+      </x:c>
+      <x:c r="J8" s="181" t="str">
+        <x:v>比较基数为2025年末</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="180" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B9" s="176" t="str">
+        <x:v>应收账款</x:v>
+      </x:c>
+      <x:c r="C9" s="178" t="n">
+        <x:v>5507.175</x:v>
+      </x:c>
+      <x:c r="D9" s="178" t="n">
+        <x:v>2012.523</x:v>
+      </x:c>
+      <x:c r="E9" s="179" t="n">
+        <x:f>IFERROR(C9/D9-1,"")</x:f>
+        <x:v>1.736453198298852</x:v>
+      </x:c>
+      <x:c r="F9" s="176" t="str">
+        <x:v>RMB m</x:v>
+      </x:c>
+      <x:c r="G9" s="181" t="str">
+        <x:v>销售尚未完全回款，必须观察下半年回收</x:v>
+      </x:c>
+      <x:c r="H9" s="181" t="str">
+        <x:v>2026-08-29</x:v>
+      </x:c>
+      <x:c r="I9" s="181" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-08-29/1225527801.PDF</x:v>
+      </x:c>
+      <x:c r="J9" s="181" t="str">
+        <x:v>比较基数为2025年末</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="180" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B10" s="176" t="str">
+        <x:v>自产天然铀收入</x:v>
+      </x:c>
+      <x:c r="C10" s="178" t="n">
+        <x:v>1831.192</x:v>
+      </x:c>
+      <x:c r="D10" s="178" t="n">
+        <x:v>2073.4</x:v>
+      </x:c>
+      <x:c r="E10" s="179" t="n">
+        <x:f>IFERROR(C10/D10-1,"")</x:f>
+        <x:v>-0.11681682261020554</x:v>
+      </x:c>
+      <x:c r="F10" s="176" t="str">
+        <x:v>RMB m</x:v>
+      </x:c>
+      <x:c r="G10" s="181" t="str">
+        <x:v>自产业务未随总收入同步增长</x:v>
+      </x:c>
+      <x:c r="H10" s="181" t="str">
+        <x:v>2026-08-29</x:v>
+      </x:c>
+      <x:c r="I10" s="181" t="str">
+        <x:v>https://static.cninfo.com.cn/finalpage/2026-08-29/1225527801.PDF</x:v>
+      </x:c>
+      <x:c r="J10" s="181" t="str">
+        <x:v>同比-11.68%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="180" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B11" s="176" t="str">
+        <x:v>营业收入</x:v>
+      </x:c>
+      <x:c r="C11" s="178" t="n">
+        <x:v>2024.892</x:v>
+      </x:c>
+      <x:c r="D11" s="178" t="n">
+        <x:v>1709</x:v>
+      </x:c>
+      <x:c r="E11" s="179" t="n">
+        <x:f>IFERROR(C11/D11-1,"")</x:f>
+        <x:v>0.18484025746050325</x:v>
+      </x:c>
+      <x:c r="F11" s="176" t="str">
+        <x:v>HKD m</x:v>
+      </x:c>
+      <x:c r="G11" s="181" t="str">
+        <x:v>历史上下半年交付不均，收入不直接年化</x:v>
+      </x:c>
+      <x:c r="H11" s="181" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="I11" s="181" t="str">
+        <x:v>https://www1.hkexnews.hk/listedco/listconews/sehk/2026/0827/2026082702321.pdf</x:v>
+      </x:c>
+      <x:c r="J11" s="181" t="str">
+        <x:v>财报原值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="180" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B12" s="176" t="str">
+        <x:v>归母净利润</x:v>
+      </x:c>
+      <x:c r="C12" s="178" t="n">
+        <x:v>-80.056</x:v>
+      </x:c>
+      <x:c r="D12" s="178" t="n">
+        <x:v>-67.57</x:v>
+      </x:c>
+      <x:c r="E12" s="179" t="n">
+        <x:f>IFERROR(C12/D12-1,"")</x:f>
+        <x:v>0.18478614769868296</x:v>
+      </x:c>
+      <x:c r="F12" s="176" t="str">
+        <x:v>HKD m</x:v>
+      </x:c>
+      <x:c r="G12" s="181" t="str">
+        <x:v>联营矿利润与贸易毛利共同承压，2026预测下修</x:v>
+      </x:c>
+      <x:c r="H12" s="181" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="I12" s="181" t="str">
+        <x:v>https://www1.hkexnews.hk/listedco/listconews/sehk/2026/0827/2026082702321.pdf</x:v>
+      </x:c>
+      <x:c r="J12" s="181" t="str">
+        <x:v>财报原值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="180" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B13" s="176" t="str">
+        <x:v>联营+合营应占利润</x:v>
+      </x:c>
+      <x:c r="C13" s="178" t="n">
+        <x:v>137.582</x:v>
+      </x:c>
+      <x:c r="D13" s="178" t="n">
+        <x:v>305.571</x:v>
+      </x:c>
+      <x:c r="E13" s="179" t="n">
+        <x:f>IFERROR(C13/D13-1,"")</x:f>
+        <x:v>-0.549754394232437</x:v>
+      </x:c>
+      <x:c r="F13" s="176" t="str">
+        <x:v>HKD m</x:v>
+      </x:c>
+      <x:c r="G13" s="181" t="str">
+        <x:v>硫酸供应和成本抬升削弱矿山利润</x:v>
+      </x:c>
+      <x:c r="H13" s="181" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="I13" s="181" t="str">
+        <x:v>https://www1.hkexnews.hk/listedco/listconews/sehk/2026/0827/2026082702321.pdf</x:v>
+      </x:c>
+      <x:c r="J13" s="181" t="str">
+        <x:v>56.789+80.793</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="180" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B14" s="176" t="str">
+        <x:v>权益产量</x:v>
+      </x:c>
+      <x:c r="C14" s="178" t="n">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="D14" s="178"/>
+      <x:c r="E14" s="179" t="str">
+        <x:f>IFERROR(C14/D14-1,"")</x:f>
+      </x:c>
+      <x:c r="F14" s="176" t="str">
+        <x:v>tU</x:v>
+      </x:c>
+      <x:c r="G14" s="181" t="str">
+        <x:v>产量执行尚可；主要问题是成本与确认时点</x:v>
+      </x:c>
+      <x:c r="H14" s="181" t="str">
+        <x:v>2026-08-27</x:v>
+      </x:c>
+      <x:c r="I14" s="181" t="str">
+        <x:v>https://www1.hkexnews.hk/listedco/listconews/sehk/2026/0827/2026082702321.pdf</x:v>
+      </x:c>
+      <x:c r="J14" s="181" t="str">
+        <x:v>H1总计</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="180" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B15" s="176" t="str">
+        <x:v>营业收入</x:v>
+      </x:c>
+      <x:c r="C15" s="178" t="n">
+        <x:v>142.115</x:v>
+      </x:c>
+      <x:c r="D15" s="178" t="n">
+        <x:v>592.11</x:v>
+      </x:c>
+      <x:c r="E15" s="179" t="n">
+        <x:f>IFERROR(C15/D15-1,"")</x:f>
+        <x:v>-0.7599854756717501</x:v>
+      </x:c>
+      <x:c r="F15" s="176" t="str">
+        <x:v>HKD m</x:v>
+      </x:c>
+      <x:c r="G15" s="181" t="str">
+        <x:v>主动收缩高波动第三方现货交易，旧交易量假设下修</x:v>
+      </x:c>
+      <x:c r="H15" s="181" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="I15" s="181" t="str">
+        <x:v>https://www1.hkexnews.hk/listedco/listconews/sehk/2026/0826/2026082601623.pdf</x:v>
+      </x:c>
+      <x:c r="J15" s="181" t="str">
+        <x:v>财报原值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="180" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B16" s="176" t="str">
+        <x:v>归母净利润</x:v>
+      </x:c>
+      <x:c r="C16" s="178" t="n">
+        <x:v>5.276</x:v>
+      </x:c>
+      <x:c r="D16" s="178" t="n">
+        <x:v>10.359</x:v>
+      </x:c>
+      <x:c r="E16" s="179" t="n">
+        <x:f>IFERROR(C16/D16-1,"")</x:f>
+        <x:v>-0.49068442899893816</x:v>
+      </x:c>
+      <x:c r="F16" s="176" t="str">
+        <x:v>HKD m</x:v>
+      </x:c>
+      <x:c r="G16" s="181" t="str">
+        <x:v>收入下降快于利润，佣金/低风险关联交易提供缓冲</x:v>
+      </x:c>
+      <x:c r="H16" s="181" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="I16" s="181" t="str">
+        <x:v>https://www1.hkexnews.hk/listedco/listconews/sehk/2026/0826/2026082601623.pdf</x:v>
+      </x:c>
+      <x:c r="J16" s="181" t="str">
+        <x:v>财报原值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="180" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B17" s="176" t="str">
+        <x:v>毛利率</x:v>
+      </x:c>
+      <x:c r="C17" s="187" t="n">
+        <x:v>0.058</x:v>
+      </x:c>
+      <x:c r="D17" s="187" t="n">
+        <x:v>0.033</x:v>
+      </x:c>
+      <x:c r="E17" s="179" t="n">
+        <x:f>IFERROR(C17/D17-1,"")</x:f>
+        <x:v>0.7575757575757576</x:v>
+      </x:c>
+      <x:c r="F17" s="176" t="str">
+        <x:v>%</x:v>
+      </x:c>
+      <x:c r="G17" s="181" t="str">
+        <x:v>收入质量改善但绝对规模仍小</x:v>
+      </x:c>
+      <x:c r="H17" s="181" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="I17" s="181" t="str">
+        <x:v>https://www1.hkexnews.hk/listedco/listconews/sehk/2026/0826/2026082601623.pdf</x:v>
+      </x:c>
+      <x:c r="J17" s="181" t="str">
+        <x:v>财报原值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="180" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B18" s="176" t="str">
+        <x:v>现金</x:v>
+      </x:c>
+      <x:c r="C18" s="178" t="n">
+        <x:v>732.589</x:v>
+      </x:c>
+      <x:c r="D18" s="178" t="n">
+        <x:v>907.053</x:v>
+      </x:c>
+      <x:c r="E18" s="179" t="n">
+        <x:f>IFERROR(C18/D18-1,"")</x:f>
+        <x:v>-0.1923415721021814</x:v>
+      </x:c>
+      <x:c r="F18" s="176" t="str">
+        <x:v>HKD m</x:v>
+      </x:c>
+      <x:c r="G18" s="181" t="str">
+        <x:v>净现金垫仍在，但上半年现金减少</x:v>
+      </x:c>
+      <x:c r="H18" s="181" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="I18" s="181" t="str">
+        <x:v>https://www1.hkexnews.hk/listedco/listconews/sehk/2026/0826/2026082601623.pdf</x:v>
+      </x:c>
+      <x:c r="J18" s="181" t="str">
+        <x:v>比较基数为2025年末</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="165" t="str">
+        <x:v>2026H1 更新后四情景预测</x:v>
+      </x:c>
+      <x:c r="B1" s="165"/>
+      <x:c r="C1" s="165"/>
+      <x:c r="D1" s="165"/>
+      <x:c r="E1" s="165"/>
+      <x:c r="F1" s="165"/>
+      <x:c r="G1" s="165"/>
+      <x:c r="H1" s="165"/>
+      <x:c r="I1" s="165"/>
+      <x:c r="J1" s="165"/>
+      <x:c r="K1" s="165"/>
+      <x:c r="L1" s="165"/>
+      <x:c r="M1" s="165"/>
+      <x:c r="N1" s="165"/>
+      <x:c r="O1" s="165"/>
+      <x:c r="P1" s="165"/>
+      <x:c r="Q1" s="165"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="169" t="str">
+        <x:v>收入与净利润为情景输入；EPS、合理价与变动幅度由公式计算。Super Bull是压力测试，不进入标准情景排序。金额单位为百万本币，每股单位与上市地币种一致。</x:v>
+      </x:c>
+      <x:c r="B2" s="169"/>
+      <x:c r="C2" s="169"/>
+      <x:c r="D2" s="169"/>
+      <x:c r="E2" s="169"/>
+      <x:c r="F2" s="169"/>
+      <x:c r="G2" s="169"/>
+      <x:c r="H2" s="169"/>
+      <x:c r="I2" s="169"/>
+      <x:c r="J2" s="169"/>
+      <x:c r="K2" s="169"/>
+      <x:c r="L2" s="169"/>
+      <x:c r="M2" s="169"/>
+      <x:c r="N2" s="169"/>
+      <x:c r="O2" s="169"/>
+      <x:c r="P2" s="169"/>
+      <x:c r="Q2" s="169"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="174" t="str">
+        <x:v>公司</x:v>
+      </x:c>
+      <x:c r="B4" s="174" t="str">
+        <x:v>情景</x:v>
+      </x:c>
+      <x:c r="C4" s="174" t="str">
+        <x:v>年份</x:v>
+      </x:c>
+      <x:c r="D4" s="174" t="str">
+        <x:v>营业收入</x:v>
+      </x:c>
+      <x:c r="E4" s="174" t="str">
+        <x:v>收入同比</x:v>
+      </x:c>
+      <x:c r="F4" s="174" t="str">
+        <x:v>归母净利润</x:v>
+      </x:c>
+      <x:c r="G4" s="174" t="str">
+        <x:v>利润同比</x:v>
+      </x:c>
+      <x:c r="H4" s="174" t="str">
+        <x:v>期末股本(m)</x:v>
+      </x:c>
+      <x:c r="I4" s="174" t="str">
+        <x:v>EPS</x:v>
+      </x:c>
+      <x:c r="J4" s="174" t="str">
+        <x:v>估值方法</x:v>
+      </x:c>
+      <x:c r="K4" s="174" t="str">
+        <x:v>参数/PE</x:v>
+      </x:c>
+      <x:c r="L4" s="174" t="str">
+        <x:v>净现金或SOTP输入</x:v>
+      </x:c>
+      <x:c r="M4" s="174" t="str">
+        <x:v>年末合理价</x:v>
+      </x:c>
+      <x:c r="N4" s="174" t="str">
+        <x:v>旧版净利润</x:v>
+      </x:c>
+      <x:c r="O4" s="174" t="str">
+        <x:v>旧版合理价</x:v>
+      </x:c>
+      <x:c r="P4" s="174" t="str">
+        <x:v>合理价变化</x:v>
+      </x:c>
+      <x:c r="Q4" s="174" t="str">
+        <x:v>本次更新理由</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B5" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C5" s="176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D5" s="186" t="n">
+        <x:v>19919</x:v>
+      </x:c>
+      <x:c r="E5" s="179"/>
+      <x:c r="F5" s="187" t="n">
+        <x:v>1250</x:v>
+      </x:c>
+      <x:c r="G5" s="179"/>
+      <x:c r="H5" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I5" s="185" t="n">
+        <x:f>F5/H5</x:f>
+        <x:v>0.6043956044487381</x:v>
+      </x:c>
+      <x:c r="J5" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K5" s="188"/>
+      <x:c r="L5" s="188" t="n">
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="M5" s="185" t="n">
+        <x:f>L5</x:f>
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="N5" s="189" t="n">
+        <x:v>1385.881</x:v>
+      </x:c>
+      <x:c r="O5" s="189" t="n">
+        <x:v>8.857</x:v>
+      </x:c>
+      <x:c r="P5" s="179" t="n">
+        <x:f>M5/O5-1</x:f>
+        <x:v>-0.006435587670768683</x:v>
+      </x:c>
+      <x:c r="Q5" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B6" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C6" s="176" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="D6" s="186" t="n">
+        <x:v>19730</x:v>
+      </x:c>
+      <x:c r="E6" s="179" t="n">
+        <x:f>D6/D5-1</x:f>
+        <x:v>-0.009488428133942461</x:v>
+      </x:c>
+      <x:c r="F6" s="187" t="n">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="G6" s="179" t="n">
+        <x:f>F6/F5-1</x:f>
+        <x:v>-0.10399999999999998</x:v>
+      </x:c>
+      <x:c r="H6" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I6" s="185" t="n">
+        <x:f>F6/H6</x:f>
+        <x:v>0.5415384615860693</x:v>
+      </x:c>
+      <x:c r="J6" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K6" s="188"/>
+      <x:c r="L6" s="188" t="n">
+        <x:v>6.5</x:v>
+      </x:c>
+      <x:c r="M6" s="185" t="n">
+        <x:f>L6</x:f>
+        <x:v>6.5</x:v>
+      </x:c>
+      <x:c r="N6" s="189" t="n">
+        <x:v>1656.509</x:v>
+      </x:c>
+      <x:c r="O6" s="189" t="n">
+        <x:v>7.647</x:v>
+      </x:c>
+      <x:c r="P6" s="179" t="n">
+        <x:f>M6/O6-1</x:f>
+        <x:v>-0.14999346148816528</x:v>
+      </x:c>
+      <x:c r="Q6" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B7" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C7" s="176" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="D7" s="186" t="n">
+        <x:v>19984</x:v>
+      </x:c>
+      <x:c r="E7" s="179" t="n">
+        <x:f>D7/D6-1</x:f>
+        <x:v>0.012873796249366354</x:v>
+      </x:c>
+      <x:c r="F7" s="187" t="n">
+        <x:v>1050</x:v>
+      </x:c>
+      <x:c r="G7" s="179" t="n">
+        <x:f>F7/F6-1</x:f>
+        <x:v>-0.0625</x:v>
+      </x:c>
+      <x:c r="H7" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I7" s="185" t="n">
+        <x:f>F7/H7</x:f>
+        <x:v>0.50769230773694</x:v>
+      </x:c>
+      <x:c r="J7" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K7" s="188"/>
+      <x:c r="L7" s="188" t="n">
+        <x:v>5.7</x:v>
+      </x:c>
+      <x:c r="M7" s="185" t="n">
+        <x:f>L7</x:f>
+        <x:v>5.7</x:v>
+      </x:c>
+      <x:c r="N7" s="189" t="n">
+        <x:v>1665.704</x:v>
+      </x:c>
+      <x:c r="O7" s="189" t="n">
+        <x:v>6.653</x:v>
+      </x:c>
+      <x:c r="P7" s="179" t="n">
+        <x:f>M7/O7-1</x:f>
+        <x:v>-0.14324364948143686</x:v>
+      </x:c>
+      <x:c r="Q7" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B8" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C8" s="176" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="D8" s="186" t="n">
+        <x:v>20280</x:v>
+      </x:c>
+      <x:c r="E8" s="179" t="n">
+        <x:f>D8/D7-1</x:f>
+        <x:v>0.014811849479583694</x:v>
+      </x:c>
+      <x:c r="F8" s="187" t="n">
+        <x:v>1050</x:v>
+      </x:c>
+      <x:c r="G8" s="179" t="n">
+        <x:f>F8/F7-1</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I8" s="185" t="n">
+        <x:f>F8/H8</x:f>
+        <x:v>0.50769230773694</x:v>
+      </x:c>
+      <x:c r="J8" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K8" s="188"/>
+      <x:c r="L8" s="188" t="n">
+        <x:v>5.4</x:v>
+      </x:c>
+      <x:c r="M8" s="185" t="n">
+        <x:f>L8</x:f>
+        <x:v>5.4</x:v>
+      </x:c>
+      <x:c r="N8" s="189" t="n">
+        <x:v>1692.733</x:v>
+      </x:c>
+      <x:c r="O8" s="189" t="n">
+        <x:v>5.848</x:v>
+      </x:c>
+      <x:c r="P8" s="179" t="n">
+        <x:f>M8/O8-1</x:f>
+        <x:v>-0.07660738714090276</x:v>
+      </x:c>
+      <x:c r="Q8" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B9" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C9" s="176" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="D9" s="186" t="n">
+        <x:v>20582</x:v>
+      </x:c>
+      <x:c r="E9" s="179" t="n">
+        <x:f>D9/D8-1</x:f>
+        <x:v>0.014891518737672582</x:v>
+      </x:c>
+      <x:c r="F9" s="187" t="n">
+        <x:v>1060</x:v>
+      </x:c>
+      <x:c r="G9" s="179" t="n">
+        <x:f>F9/F8-1</x:f>
+        <x:v>0.00952380952380949</x:v>
+      </x:c>
+      <x:c r="H9" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I9" s="185" t="n">
+        <x:f>F9/H9</x:f>
+        <x:v>0.5125274725725298</x:v>
+      </x:c>
+      <x:c r="J9" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K9" s="188"/>
+      <x:c r="L9" s="188" t="n">
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="M9" s="185" t="n">
+        <x:f>L9</x:f>
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="N9" s="189" t="n">
+        <x:v>1725.521</x:v>
+      </x:c>
+      <x:c r="O9" s="189" t="n">
+        <x:v>4.913</x:v>
+      </x:c>
+      <x:c r="P9" s="179" t="n">
+        <x:f>M9/O9-1</x:f>
+        <x:v>0.058416446163240376</x:v>
+      </x:c>
+      <x:c r="Q9" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B10" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C10" s="176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D10" s="186" t="n">
+        <x:v>21166</x:v>
+      </x:c>
+      <x:c r="E10" s="179"/>
+      <x:c r="F10" s="187" t="n">
+        <x:v>1980</x:v>
+      </x:c>
+      <x:c r="G10" s="179"/>
+      <x:c r="H10" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I10" s="185" t="n">
+        <x:f>F10/H10</x:f>
+        <x:v>0.9573626374468011</x:v>
+      </x:c>
+      <x:c r="J10" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K10" s="188"/>
+      <x:c r="L10" s="188" t="n">
+        <x:v>18.5</x:v>
+      </x:c>
+      <x:c r="M10" s="185" t="n">
+        <x:f>L10</x:f>
+        <x:v>18.5</x:v>
+      </x:c>
+      <x:c r="N10" s="189" t="n">
+        <x:v>1819.47</x:v>
+      </x:c>
+      <x:c r="O10" s="189" t="n">
+        <x:v>18.72</x:v>
+      </x:c>
+      <x:c r="P10" s="179" t="n">
+        <x:f>M10/O10-1</x:f>
+        <x:v>-0.01175213675213671</x:v>
+      </x:c>
+      <x:c r="Q10" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B11" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C11" s="176" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="D11" s="186" t="n">
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="E11" s="179" t="n">
+        <x:f>D11/D10-1</x:f>
+        <x:v>0.08664839837475191</x:v>
+      </x:c>
+      <x:c r="F11" s="187" t="n">
+        <x:v>2050</x:v>
+      </x:c>
+      <x:c r="G11" s="179" t="n">
+        <x:f>F11/F10-1</x:f>
+        <x:v>0.03535353535353525</x:v>
+      </x:c>
+      <x:c r="H11" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I11" s="185" t="n">
+        <x:f>F11/H11</x:f>
+        <x:v>0.9912087912959304</x:v>
+      </x:c>
+      <x:c r="J11" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K11" s="188"/>
+      <x:c r="L11" s="188" t="n">
+        <x:v>19.2</x:v>
+      </x:c>
+      <x:c r="M11" s="185" t="n">
+        <x:f>L11</x:f>
+        <x:v>19.2</x:v>
+      </x:c>
+      <x:c r="N11" s="189" t="n">
+        <x:v>2060.249</x:v>
+      </x:c>
+      <x:c r="O11" s="189" t="n">
+        <x:v>20.179</x:v>
+      </x:c>
+      <x:c r="P11" s="179" t="n">
+        <x:f>M11/O11-1</x:f>
+        <x:v>-0.04851578373556664</x:v>
+      </x:c>
+      <x:c r="Q11" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B12" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C12" s="176" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="D12" s="186" t="n">
+        <x:v>24800</x:v>
+      </x:c>
+      <x:c r="E12" s="179" t="n">
+        <x:f>D12/D11-1</x:f>
+        <x:v>0.07826086956521738</x:v>
+      </x:c>
+      <x:c r="F12" s="187" t="n">
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="G12" s="179" t="n">
+        <x:f>F12/F11-1</x:f>
+        <x:v>0.07317073170731714</x:v>
+      </x:c>
+      <x:c r="H12" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I12" s="185" t="n">
+        <x:f>F12/H12</x:f>
+        <x:v>1.063736263829779</x:v>
+      </x:c>
+      <x:c r="J12" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K12" s="188"/>
+      <x:c r="L12" s="188" t="n">
+        <x:v>20.2</x:v>
+      </x:c>
+      <x:c r="M12" s="185" t="n">
+        <x:f>L12</x:f>
+        <x:v>20.2</x:v>
+      </x:c>
+      <x:c r="N12" s="189" t="n">
+        <x:v>2198.941</x:v>
+      </x:c>
+      <x:c r="O12" s="189" t="n">
+        <x:v>21.053</x:v>
+      </x:c>
+      <x:c r="P12" s="179" t="n">
+        <x:f>M12/O12-1</x:f>
+        <x:v>-0.040516790956158344</x:v>
+      </x:c>
+      <x:c r="Q12" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B13" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C13" s="176" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="D13" s="186" t="n">
+        <x:v>26500</x:v>
+      </x:c>
+      <x:c r="E13" s="179" t="n">
+        <x:f>D13/D12-1</x:f>
+        <x:v>0.06854838709677424</x:v>
+      </x:c>
+      <x:c r="F13" s="187" t="n">
+        <x:v>2360</x:v>
+      </x:c>
+      <x:c r="G13" s="179" t="n">
+        <x:f>F13/F12-1</x:f>
+        <x:v>0.07272727272727275</x:v>
+      </x:c>
+      <x:c r="H13" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I13" s="185" t="n">
+        <x:f>F13/H13</x:f>
+        <x:v>1.1410989011992174</x:v>
+      </x:c>
+      <x:c r="J13" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K13" s="188"/>
+      <x:c r="L13" s="188" t="n">
+        <x:v>21.1</x:v>
+      </x:c>
+      <x:c r="M13" s="185" t="n">
+        <x:f>L13</x:f>
+        <x:v>21.1</x:v>
+      </x:c>
+      <x:c r="N13" s="189" t="n">
+        <x:v>2348.961</x:v>
+      </x:c>
+      <x:c r="O13" s="189" t="n">
+        <x:v>21.564</x:v>
+      </x:c>
+      <x:c r="P13" s="179" t="n">
+        <x:f>M13/O13-1</x:f>
+        <x:v>-0.021517343721016435</x:v>
+      </x:c>
+      <x:c r="Q13" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B14" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C14" s="176" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="D14" s="186" t="n">
+        <x:v>28235</x:v>
+      </x:c>
+      <x:c r="E14" s="179" t="n">
+        <x:f>D14/D13-1</x:f>
+        <x:v>0.06547169811320752</x:v>
+      </x:c>
+      <x:c r="F14" s="187" t="n">
+        <x:v>2480</x:v>
+      </x:c>
+      <x:c r="G14" s="179" t="n">
+        <x:f>F14/F13-1</x:f>
+        <x:v>0.05084745762711873</x:v>
+      </x:c>
+      <x:c r="H14" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I14" s="185" t="n">
+        <x:f>F14/H14</x:f>
+        <x:v>1.1991208792262964</x:v>
+      </x:c>
+      <x:c r="J14" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K14" s="188"/>
+      <x:c r="L14" s="188" t="n">
+        <x:v>21.6</x:v>
+      </x:c>
+      <x:c r="M14" s="185" t="n">
+        <x:f>L14</x:f>
+        <x:v>21.6</x:v>
+      </x:c>
+      <x:c r="N14" s="189" t="n">
+        <x:v>2500.569</x:v>
+      </x:c>
+      <x:c r="O14" s="189" t="n">
+        <x:v>21.623</x:v>
+      </x:c>
+      <x:c r="P14" s="179" t="n">
+        <x:f>M14/O14-1</x:f>
+        <x:v>-0.0010636821902603177</x:v>
+      </x:c>
+      <x:c r="Q14" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B15" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C15" s="176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D15" s="186" t="n">
+        <x:v>23200</x:v>
+      </x:c>
+      <x:c r="E15" s="179"/>
+      <x:c r="F15" s="187" t="n">
+        <x:v>2450</x:v>
+      </x:c>
+      <x:c r="G15" s="179"/>
+      <x:c r="H15" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I15" s="185" t="n">
+        <x:f>F15/H15</x:f>
+        <x:v>1.1846153847195267</x:v>
+      </x:c>
+      <x:c r="J15" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K15" s="188"/>
+      <x:c r="L15" s="188" t="n">
+        <x:v>23.3</x:v>
+      </x:c>
+      <x:c r="M15" s="185" t="n">
+        <x:f>L15</x:f>
+        <x:v>23.3</x:v>
+      </x:c>
+      <x:c r="N15" s="189" t="n">
+        <x:v>2249.167</x:v>
+      </x:c>
+      <x:c r="O15" s="189" t="n">
+        <x:v>23.925</x:v>
+      </x:c>
+      <x:c r="P15" s="179" t="n">
+        <x:f>M15/O15-1</x:f>
+        <x:v>-0.02612330198537094</x:v>
+      </x:c>
+      <x:c r="Q15" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B16" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C16" s="176" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="D16" s="186" t="n">
+        <x:v>26500</x:v>
+      </x:c>
+      <x:c r="E16" s="179" t="n">
+        <x:f>D16/D15-1</x:f>
+        <x:v>0.14224137931034475</x:v>
+      </x:c>
+      <x:c r="F16" s="187" t="n">
+        <x:v>2900</x:v>
+      </x:c>
+      <x:c r="G16" s="179" t="n">
+        <x:f>F16/F15-1</x:f>
+        <x:v>0.18367346938775508</x:v>
+      </x:c>
+      <x:c r="H16" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I16" s="185" t="n">
+        <x:f>F16/H16</x:f>
+        <x:v>1.4021978023210724</x:v>
+      </x:c>
+      <x:c r="J16" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K16" s="188"/>
+      <x:c r="L16" s="188" t="n">
+        <x:v>25.3</x:v>
+      </x:c>
+      <x:c r="M16" s="185" t="n">
+        <x:f>L16</x:f>
+        <x:v>25.3</x:v>
+      </x:c>
+      <x:c r="N16" s="189" t="n">
+        <x:v>2805.64</x:v>
+      </x:c>
+      <x:c r="O16" s="189" t="n">
+        <x:v>26.442</x:v>
+      </x:c>
+      <x:c r="P16" s="179" t="n">
+        <x:f>M16/O16-1</x:f>
+        <x:v>-0.04318886619771578</x:v>
+      </x:c>
+      <x:c r="Q16" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B17" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C17" s="176" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="D17" s="186" t="n">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="E17" s="179" t="n">
+        <x:f>D17/D16-1</x:f>
+        <x:v>0.13207547169811318</x:v>
+      </x:c>
+      <x:c r="F17" s="187" t="n">
+        <x:v>3250</x:v>
+      </x:c>
+      <x:c r="G17" s="179" t="n">
+        <x:f>F17/F16-1</x:f>
+        <x:v>0.1206896551724137</x:v>
+      </x:c>
+      <x:c r="H17" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I17" s="185" t="n">
+        <x:f>F17/H17</x:f>
+        <x:v>1.571428571566719</x:v>
+      </x:c>
+      <x:c r="J17" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K17" s="188"/>
+      <x:c r="L17" s="188" t="n">
+        <x:v>26.5</x:v>
+      </x:c>
+      <x:c r="M17" s="185" t="n">
+        <x:f>L17</x:f>
+        <x:v>26.5</x:v>
+      </x:c>
+      <x:c r="N17" s="189" t="n">
+        <x:v>3184.694</x:v>
+      </x:c>
+      <x:c r="O17" s="189" t="n">
+        <x:v>28.108</x:v>
+      </x:c>
+      <x:c r="P17" s="179" t="n">
+        <x:f>M17/O17-1</x:f>
+        <x:v>-0.05720791233812439</x:v>
+      </x:c>
+      <x:c r="Q17" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B18" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C18" s="176" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="D18" s="186" t="n">
+        <x:v>33000</x:v>
+      </x:c>
+      <x:c r="E18" s="179" t="n">
+        <x:f>D18/D17-1</x:f>
+        <x:v>0.10000000000000009</x:v>
+      </x:c>
+      <x:c r="F18" s="187" t="n">
+        <x:v>3650</x:v>
+      </x:c>
+      <x:c r="G18" s="179" t="n">
+        <x:f>F18/F17-1</x:f>
+        <x:v>0.12307692307692308</x:v>
+      </x:c>
+      <x:c r="H18" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I18" s="185" t="n">
+        <x:f>F18/H18</x:f>
+        <x:v>1.7648351649903151</x:v>
+      </x:c>
+      <x:c r="J18" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K18" s="188"/>
+      <x:c r="L18" s="188" t="n">
+        <x:v>26.8</x:v>
+      </x:c>
+      <x:c r="M18" s="185" t="n">
+        <x:f>L18</x:f>
+        <x:v>26.8</x:v>
+      </x:c>
+      <x:c r="N18" s="189" t="n">
+        <x:v>3630.465</x:v>
+      </x:c>
+      <x:c r="O18" s="189" t="n">
+        <x:v>29.184</x:v>
+      </x:c>
+      <x:c r="P18" s="179" t="n">
+        <x:f>M18/O18-1</x:f>
+        <x:v>-0.08168859649122806</x:v>
+      </x:c>
+      <x:c r="Q18" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B19" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C19" s="176" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="D19" s="186" t="n">
+        <x:v>35800</x:v>
+      </x:c>
+      <x:c r="E19" s="179" t="n">
+        <x:f>D19/D18-1</x:f>
+        <x:v>0.08484848484848495</x:v>
+      </x:c>
+      <x:c r="F19" s="187" t="n">
+        <x:v>4100</x:v>
+      </x:c>
+      <x:c r="G19" s="179" t="n">
+        <x:f>F19/F18-1</x:f>
+        <x:v>0.12328767123287676</x:v>
+      </x:c>
+      <x:c r="H19" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I19" s="185" t="n">
+        <x:f>F19/H19</x:f>
+        <x:v>1.9824175825918608</x:v>
+      </x:c>
+      <x:c r="J19" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K19" s="188"/>
+      <x:c r="L19" s="188" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="M19" s="185" t="n">
+        <x:f>L19</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N19" s="189" t="n">
+        <x:v>4130.575</x:v>
+      </x:c>
+      <x:c r="O19" s="189" t="n">
+        <x:v>30.824</x:v>
+      </x:c>
+      <x:c r="P19" s="179" t="n">
+        <x:f>M19/O19-1</x:f>
+        <x:v>-0.026732416298987816</x:v>
+      </x:c>
+      <x:c r="Q19" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B20" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C20" s="176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D20" s="186" t="n">
+        <x:v>22316</x:v>
+      </x:c>
+      <x:c r="E20" s="179"/>
+      <x:c r="F20" s="187" t="n">
+        <x:v>2278</x:v>
+      </x:c>
+      <x:c r="G20" s="179"/>
+      <x:c r="H20" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I20" s="185" t="n">
+        <x:f>F20/H20</x:f>
+        <x:v>1.1014505495473803</x:v>
+      </x:c>
+      <x:c r="J20" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K20" s="188"/>
+      <x:c r="L20" s="188" t="n">
+        <x:v>88.82</x:v>
+      </x:c>
+      <x:c r="M20" s="185" t="n">
+        <x:f>L20</x:f>
+        <x:v>88.82</x:v>
+      </x:c>
+      <x:c r="N20" s="189" t="n">
+        <x:v>2278</x:v>
+      </x:c>
+      <x:c r="O20" s="189" t="n">
+        <x:v>88.82</x:v>
+      </x:c>
+      <x:c r="P20" s="179" t="n">
+        <x:f>M20/O20-1</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q20" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B21" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C21" s="176" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="D21" s="186" t="n">
+        <x:v>28100</x:v>
+      </x:c>
+      <x:c r="E21" s="179" t="n">
+        <x:f>D21/D20-1</x:f>
+        <x:v>0.25918623409213115</x:v>
+      </x:c>
+      <x:c r="F21" s="187" t="n">
+        <x:v>3109</x:v>
+      </x:c>
+      <x:c r="G21" s="179" t="n">
+        <x:f>F21/F20-1</x:f>
+        <x:v>0.36479367866549595</x:v>
+      </x:c>
+      <x:c r="H21" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I21" s="185" t="n">
+        <x:f>F21/H21</x:f>
+        <x:v>1.5032527473849013</x:v>
+      </x:c>
+      <x:c r="J21" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K21" s="188"/>
+      <x:c r="L21" s="188" t="n">
+        <x:v>60.599</x:v>
+      </x:c>
+      <x:c r="M21" s="185" t="n">
+        <x:f>L21</x:f>
+        <x:v>60.599</x:v>
+      </x:c>
+      <x:c r="N21" s="189" t="n">
+        <x:v>3109</x:v>
+      </x:c>
+      <x:c r="O21" s="189" t="n">
+        <x:v>60.599</x:v>
+      </x:c>
+      <x:c r="P21" s="179" t="n">
+        <x:f>M21/O21-1</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q21" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B22" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C22" s="176" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="D22" s="186" t="n">
+        <x:v>34058</x:v>
+      </x:c>
+      <x:c r="E22" s="179" t="n">
+        <x:f>D22/D21-1</x:f>
+        <x:v>0.21202846975088963</x:v>
+      </x:c>
+      <x:c r="F22" s="187" t="n">
+        <x:v>3903</x:v>
+      </x:c>
+      <x:c r="G22" s="179" t="n">
+        <x:f>F22/F21-1</x:f>
+        <x:v>0.25538758443229326</x:v>
+      </x:c>
+      <x:c r="H22" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I22" s="185" t="n">
+        <x:f>F22/H22</x:f>
+        <x:v>1.8871648353307398</x:v>
+      </x:c>
+      <x:c r="J22" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K22" s="188"/>
+      <x:c r="L22" s="188" t="n">
+        <x:v>50.723</x:v>
+      </x:c>
+      <x:c r="M22" s="185" t="n">
+        <x:f>L22</x:f>
+        <x:v>50.723</x:v>
+      </x:c>
+      <x:c r="N22" s="189" t="n">
+        <x:v>3903</x:v>
+      </x:c>
+      <x:c r="O22" s="189" t="n">
+        <x:v>50.723</x:v>
+      </x:c>
+      <x:c r="P22" s="179" t="n">
+        <x:f>M22/O22-1</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q22" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B23" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C23" s="176" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="D23" s="186" t="n">
+        <x:v>39005</x:v>
+      </x:c>
+      <x:c r="E23" s="179" t="n">
+        <x:f>D23/D22-1</x:f>
+        <x:v>0.14525221680662392</x:v>
+      </x:c>
+      <x:c r="F23" s="187" t="n">
+        <x:v>4668</x:v>
+      </x:c>
+      <x:c r="G23" s="179" t="n">
+        <x:f>F23/F22-1</x:f>
+        <x:v>0.19600307455803234</x:v>
+      </x:c>
+      <x:c r="H23" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I23" s="185" t="n">
+        <x:f>F23/H23</x:f>
+        <x:v>2.2570549452533673</x:v>
+      </x:c>
+      <x:c r="J23" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K23" s="188"/>
+      <x:c r="L23" s="188" t="n">
+        <x:v>47.255</x:v>
+      </x:c>
+      <x:c r="M23" s="185" t="n">
+        <x:f>L23</x:f>
+        <x:v>47.255</x:v>
+      </x:c>
+      <x:c r="N23" s="189" t="n">
+        <x:v>4668</x:v>
+      </x:c>
+      <x:c r="O23" s="189" t="n">
+        <x:v>47.255</x:v>
+      </x:c>
+      <x:c r="P23" s="179" t="n">
+        <x:f>M23/O23-1</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q23" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B24" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C24" s="176" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="D24" s="186" t="n">
+        <x:v>43889</x:v>
+      </x:c>
+      <x:c r="E24" s="179" t="n">
+        <x:f>D24/D23-1</x:f>
+        <x:v>0.12521471606204337</x:v>
+      </x:c>
+      <x:c r="F24" s="187" t="n">
+        <x:v>5648</x:v>
+      </x:c>
+      <x:c r="G24" s="179" t="n">
+        <x:f>F24/F23-1</x:f>
+        <x:v>0.20994001713796062</x:v>
+      </x:c>
+      <x:c r="H24" s="178" t="n">
+        <x:v>2068.181818</x:v>
+      </x:c>
+      <x:c r="I24" s="185" t="n">
+        <x:f>F24/H24</x:f>
+        <x:v>2.730901099141178</x:v>
+      </x:c>
+      <x:c r="J24" s="176" t="str">
+        <x:v>SOTP后每股权益价值</x:v>
+      </x:c>
+      <x:c r="K24" s="188"/>
+      <x:c r="L24" s="188" t="n">
+        <x:v>40.963</x:v>
+      </x:c>
+      <x:c r="M24" s="185" t="n">
+        <x:f>L24</x:f>
+        <x:v>40.963</x:v>
+      </x:c>
+      <x:c r="N24" s="189" t="n">
+        <x:v>5648</x:v>
+      </x:c>
+      <x:c r="O24" s="189" t="n">
+        <x:v>40.963</x:v>
+      </x:c>
+      <x:c r="P24" s="179" t="n">
+        <x:f>M24/O24-1</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q24" s="181" t="str">
+        <x:v>H1总收入与利润较稳；自产收入/毛利偏弱，应收上升限制估值上修</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B25" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C25" s="176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D25" s="186" t="n">
+        <x:v>6654</x:v>
+      </x:c>
+      <x:c r="E25" s="179"/>
+      <x:c r="F25" s="187" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G25" s="179"/>
+      <x:c r="H25" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I25" s="185" t="n">
+        <x:f>F25/H25</x:f>
+        <x:v>0.03289178244594371</x:v>
+      </x:c>
+      <x:c r="J25" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K25" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L25" s="188" t="n">
+        <x:v>0.695739</x:v>
+      </x:c>
+      <x:c r="M25" s="185" t="n">
+        <x:f>L25*K25*(0.6+0.4*F25/N25)</x:f>
+        <x:v>0.49598796540984463</x:v>
+      </x:c>
+      <x:c r="N25" s="189" t="n">
+        <x:v>520.551</x:v>
+      </x:c>
+      <x:c r="O25" s="189" t="n">
+        <x:v>0.695739</x:v>
+      </x:c>
+      <x:c r="P25" s="179" t="n">
+        <x:f>M25/O25-1</x:f>
+        <x:v>-0.287106277771054</x:v>
+      </x:c>
+      <x:c r="Q25" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B26" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C26" s="176" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="D26" s="186" t="n">
+        <x:v>7604</x:v>
+      </x:c>
+      <x:c r="E26" s="179" t="n">
+        <x:f>D26/D25-1</x:f>
+        <x:v>0.1427712654042681</x:v>
+      </x:c>
+      <x:c r="F26" s="187" t="n">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="G26" s="179" t="n">
+        <x:f>F26/F25-1</x:f>
+        <x:v>1.48</x:v>
+      </x:c>
+      <x:c r="H26" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I26" s="185" t="n">
+        <x:f>F26/H26</x:f>
+        <x:v>0.0815716204659404</x:v>
+      </x:c>
+      <x:c r="J26" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K26" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L26" s="188" t="n">
+        <x:v>0.687345</x:v>
+      </x:c>
+      <x:c r="M26" s="185" t="n">
+        <x:f>L26*K26*(0.6+0.4*F26/N26)</x:f>
+        <x:v>0.5653207423239497</x:v>
+      </x:c>
+      <x:c r="N26" s="189" t="n">
+        <x:v>790.172</x:v>
+      </x:c>
+      <x:c r="O26" s="189" t="n">
+        <x:v>0.687345</x:v>
+      </x:c>
+      <x:c r="P26" s="179" t="n">
+        <x:f>M26/O26-1</x:f>
+        <x:v>-0.177529854259579</x:v>
+      </x:c>
+      <x:c r="Q26" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B27" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C27" s="176" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="D27" s="186" t="n">
+        <x:v>7973</x:v>
+      </x:c>
+      <x:c r="E27" s="179" t="n">
+        <x:f>D27/D26-1</x:f>
+        <x:v>0.0485270910047344</x:v>
+      </x:c>
+      <x:c r="F27" s="187" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="G27" s="179" t="n">
+        <x:f>F27/F26-1</x:f>
+        <x:v>0.048387096774193505</x:v>
+      </x:c>
+      <x:c r="H27" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I27" s="185" t="n">
+        <x:f>F27/H27</x:f>
+        <x:v>0.08551863435945364</x:v>
+      </x:c>
+      <x:c r="J27" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K27" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L27" s="188" t="n">
+        <x:v>0.664178</x:v>
+      </x:c>
+      <x:c r="M27" s="185" t="n">
+        <x:f>L27*K27*(0.6+0.4*F27/N27)</x:f>
+        <x:v>0.5488427386971126</x:v>
+      </x:c>
+      <x:c r="N27" s="189" t="n">
+        <x:v>817.185</x:v>
+      </x:c>
+      <x:c r="O27" s="189" t="n">
+        <x:v>0.664178</x:v>
+      </x:c>
+      <x:c r="P27" s="179" t="n">
+        <x:f>M27/O27-1</x:f>
+        <x:v>-0.17365113162870105</x:v>
+      </x:c>
+      <x:c r="Q27" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B28" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C28" s="176" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="D28" s="186" t="n">
+        <x:v>8100</x:v>
+      </x:c>
+      <x:c r="E28" s="179" t="n">
+        <x:f>D28/D27-1</x:f>
+        <x:v>0.015928759563526906</x:v>
+      </x:c>
+      <x:c r="F28" s="187" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="G28" s="179" t="n">
+        <x:f>F28/F27-1</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I28" s="185" t="n">
+        <x:f>F28/H28</x:f>
+        <x:v>0.08551863435945364</x:v>
+      </x:c>
+      <x:c r="J28" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K28" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L28" s="188" t="n">
+        <x:v>0.626505</x:v>
+      </x:c>
+      <x:c r="M28" s="185" t="n">
+        <x:f>L28*K28*(0.6+0.4*F28/N28)</x:f>
+        <x:v>0.5191953969630418</x:v>
+      </x:c>
+      <x:c r="N28" s="189" t="n">
+        <x:v>810.482</x:v>
+      </x:c>
+      <x:c r="O28" s="189" t="n">
+        <x:v>0.626505</x:v>
+      </x:c>
+      <x:c r="P28" s="179" t="n">
+        <x:f>M28/O28-1</x:f>
+        <x:v>-0.17128291559837217</x:v>
+      </x:c>
+      <x:c r="Q28" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B29" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C29" s="176" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="D29" s="186" t="n">
+        <x:v>8158</x:v>
+      </x:c>
+      <x:c r="E29" s="179" t="n">
+        <x:f>D29/D28-1</x:f>
+        <x:v>0.007160493827160552</x:v>
+      </x:c>
+      <x:c r="F29" s="187" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="G29" s="179" t="n">
+        <x:f>F29/F28-1</x:f>
+        <x:v>-0.03076923076923077</x:v>
+      </x:c>
+      <x:c r="H29" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I29" s="185" t="n">
+        <x:f>F29/H29</x:f>
+        <x:v>0.08288729176377815</x:v>
+      </x:c>
+      <x:c r="J29" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K29" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L29" s="188" t="n">
+        <x:v>0.538715</x:v>
+      </x:c>
+      <x:c r="M29" s="185" t="n">
+        <x:f>L29*K29*(0.6+0.4*F29/N29)</x:f>
+        <x:v>0.44565240234284165</x:v>
+      </x:c>
+      <x:c r="N29" s="189" t="n">
+        <x:v>789.554</x:v>
+      </x:c>
+      <x:c r="O29" s="189" t="n">
+        <x:v>0.538715</x:v>
+      </x:c>
+      <x:c r="P29" s="179" t="n">
+        <x:f>M29/O29-1</x:f>
+        <x:v>-0.17274922297904904</x:v>
+      </x:c>
+      <x:c r="Q29" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B30" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C30" s="176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D30" s="186" t="n">
+        <x:v>7972</x:v>
+      </x:c>
+      <x:c r="E30" s="179"/>
+      <x:c r="F30" s="187" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="G30" s="179"/>
+      <x:c r="H30" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I30" s="185" t="n">
+        <x:f>F30/H30</x:f>
+        <x:v>0.06578356489188741</x:v>
+      </x:c>
+      <x:c r="J30" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K30" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L30" s="188" t="n">
+        <x:v>1.143762</x:v>
+      </x:c>
+      <x:c r="M30" s="185" t="n">
+        <x:f>L30*K30*(0.6+0.4*F30/N30)</x:f>
+        <x:v>0.8806173328827545</x:v>
+      </x:c>
+      <x:c r="N30" s="189" t="n">
+        <x:v>782.845</x:v>
+      </x:c>
+      <x:c r="O30" s="189" t="n">
+        <x:v>1.143762</x:v>
+      </x:c>
+      <x:c r="P30" s="179" t="n">
+        <x:f>M30/O30-1</x:f>
+        <x:v>-0.230069426259349</x:v>
+      </x:c>
+      <x:c r="Q30" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B31" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C31" s="176" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="D31" s="186" t="n">
+        <x:v>9904</x:v>
+      </x:c>
+      <x:c r="E31" s="179" t="n">
+        <x:f>D31/D30-1</x:f>
+        <x:v>0.2423482187656798</x:v>
+      </x:c>
+      <x:c r="F31" s="187" t="n">
+        <x:v>950</x:v>
+      </x:c>
+      <x:c r="G31" s="179" t="n">
+        <x:f>F31/F30-1</x:f>
+        <x:v>0.8999999999999999</x:v>
+      </x:c>
+      <x:c r="H31" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I31" s="185" t="n">
+        <x:f>F31/H31</x:f>
+        <x:v>0.1249887732945861</x:v>
+      </x:c>
+      <x:c r="J31" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K31" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L31" s="188" t="n">
+        <x:v>1.15326</x:v>
+      </x:c>
+      <x:c r="M31" s="185" t="n">
+        <x:f>L31*K31*(0.6+0.4*F31/N31)</x:f>
+        <x:v>0.9655179820514446</x:v>
+      </x:c>
+      <x:c r="N31" s="189" t="n">
+        <x:v>1150.711</x:v>
+      </x:c>
+      <x:c r="O31" s="189" t="n">
+        <x:v>1.15326</x:v>
+      </x:c>
+      <x:c r="P31" s="179" t="n">
+        <x:f>M31/O31-1</x:f>
+        <x:v>-0.16279244745205368</x:v>
+      </x:c>
+      <x:c r="Q31" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B32" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C32" s="176" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="D32" s="186" t="n">
+        <x:v>10592</x:v>
+      </x:c>
+      <x:c r="E32" s="179" t="n">
+        <x:f>D32/D31-1</x:f>
+        <x:v>0.06946688206785145</x:v>
+      </x:c>
+      <x:c r="F32" s="187" t="n">
+        <x:v>1050</x:v>
+      </x:c>
+      <x:c r="G32" s="179" t="n">
+        <x:f>F32/F31-1</x:f>
+        <x:v>0.10526315789473695</x:v>
+      </x:c>
+      <x:c r="H32" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I32" s="185" t="n">
+        <x:f>F32/H32</x:f>
+        <x:v>0.13814548627296358</x:v>
+      </x:c>
+      <x:c r="J32" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K32" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L32" s="188" t="n">
+        <x:v>1.064714</x:v>
+      </x:c>
+      <x:c r="M32" s="185" t="n">
+        <x:f>L32*K32*(0.6+0.4*F32/N32)</x:f>
+        <x:v>0.9099178957398136</x:v>
+      </x:c>
+      <x:c r="N32" s="189" t="n">
+        <x:v>1201.478</x:v>
+      </x:c>
+      <x:c r="O32" s="189" t="n">
+        <x:v>1.064714</x:v>
+      </x:c>
+      <x:c r="P32" s="179" t="n">
+        <x:f>M32/O32-1</x:f>
+        <x:v>-0.14538749773196025</x:v>
+      </x:c>
+      <x:c r="Q32" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B33" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C33" s="176" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="D33" s="186" t="n">
+        <x:v>10951</x:v>
+      </x:c>
+      <x:c r="E33" s="179" t="n">
+        <x:f>D33/D32-1</x:f>
+        <x:v>0.03389350453172213</x:v>
+      </x:c>
+      <x:c r="F33" s="187" t="n">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="G33" s="179" t="n">
+        <x:f>F33/F32-1</x:f>
+        <x:v>0.04761904761904767</x:v>
+      </x:c>
+      <x:c r="H33" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I33" s="185" t="n">
+        <x:f>F33/H33</x:f>
+        <x:v>0.14472384276215233</x:v>
+      </x:c>
+      <x:c r="J33" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K33" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L33" s="188" t="n">
+        <x:v>1.031969</x:v>
+      </x:c>
+      <x:c r="M33" s="185" t="n">
+        <x:f>L33*K33*(0.6+0.4*F33/N33)</x:f>
+        <x:v>0.8908151121420596</x:v>
+      </x:c>
+      <x:c r="N33" s="189" t="n">
+        <x:v>1225.176</x:v>
+      </x:c>
+      <x:c r="O33" s="189" t="n">
+        <x:v>1.031969</x:v>
+      </x:c>
+      <x:c r="P33" s="179" t="n">
+        <x:f>M33/O33-1</x:f>
+        <x:v>-0.1367811318537091</x:v>
+      </x:c>
+      <x:c r="Q33" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B34" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C34" s="176" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="D34" s="186" t="n">
+        <x:v>11329</x:v>
+      </x:c>
+      <x:c r="E34" s="179" t="n">
+        <x:f>D34/D33-1</x:f>
+        <x:v>0.03451739567162826</x:v>
+      </x:c>
+      <x:c r="F34" s="187" t="n">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="G34" s="179" t="n">
+        <x:f>F34/F33-1</x:f>
+        <x:v>0.018181818181818077</x:v>
+      </x:c>
+      <x:c r="H34" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I34" s="185" t="n">
+        <x:f>F34/H34</x:f>
+        <x:v>0.14735518535782782</x:v>
+      </x:c>
+      <x:c r="J34" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K34" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L34" s="188" t="n">
+        <x:v>1.009463</x:v>
+      </x:c>
+      <x:c r="M34" s="185" t="n">
+        <x:f>L34*K34*(0.6+0.4*F34/N34)</x:f>
+        <x:v>0.8742132692656102</x:v>
+      </x:c>
+      <x:c r="N34" s="189" t="n">
+        <x:v>1236.741</x:v>
+      </x:c>
+      <x:c r="O34" s="189" t="n">
+        <x:v>1.009463</x:v>
+      </x:c>
+      <x:c r="P34" s="179" t="n">
+        <x:f>M34/O34-1</x:f>
+        <x:v>-0.13398186038952375</x:v>
+      </x:c>
+      <x:c r="Q34" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B35" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C35" s="176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D35" s="186" t="n">
+        <x:v>9849</x:v>
+      </x:c>
+      <x:c r="E35" s="179"/>
+      <x:c r="F35" s="187" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="G35" s="179"/>
+      <x:c r="H35" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I35" s="185" t="n">
+        <x:f>F35/H35</x:f>
+        <x:v>0.09867534733783113</x:v>
+      </x:c>
+      <x:c r="J35" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K35" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L35" s="188" t="n">
+        <x:v>1.653745</x:v>
+      </x:c>
+      <x:c r="M35" s="185" t="n">
+        <x:f>L35*K35*(0.6+0.4*F35/N35)</x:f>
+        <x:v>1.3220806437512311</x:v>
+      </x:c>
+      <x:c r="N35" s="189" t="n">
+        <x:v>1040.677</x:v>
+      </x:c>
+      <x:c r="O35" s="189" t="n">
+        <x:v>1.653745</x:v>
+      </x:c>
+      <x:c r="P35" s="179" t="n">
+        <x:f>M35/O35-1</x:f>
+        <x:v>-0.20055350507410086</x:v>
+      </x:c>
+      <x:c r="Q35" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B36" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C36" s="176" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="D36" s="186" t="n">
+        <x:v>14503</x:v>
+      </x:c>
+      <x:c r="E36" s="179" t="n">
+        <x:f>D36/D35-1</x:f>
+        <x:v>0.47253528276982437</x:v>
+      </x:c>
+      <x:c r="F36" s="187" t="n">
+        <x:v>1450</x:v>
+      </x:c>
+      <x:c r="G36" s="179" t="n">
+        <x:f>F36/F35-1</x:f>
+        <x:v>0.9333333333333333</x:v>
+      </x:c>
+      <x:c r="H36" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I36" s="185" t="n">
+        <x:f>F36/H36</x:f>
+        <x:v>0.19077233818647352</x:v>
+      </x:c>
+      <x:c r="J36" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K36" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L36" s="188" t="n">
+        <x:v>1.667326</x:v>
+      </x:c>
+      <x:c r="M36" s="185" t="n">
+        <x:f>L36*K36*(0.6+0.4*F36/N36)</x:f>
+        <x:v>1.397697556223208</x:v>
+      </x:c>
+      <x:c r="N36" s="189" t="n">
+        <x:v>1749.993</x:v>
+      </x:c>
+      <x:c r="O36" s="189" t="n">
+        <x:v>1.667326</x:v>
+      </x:c>
+      <x:c r="P36" s="179" t="n">
+        <x:f>M36/O36-1</x:f>
+        <x:v>-0.1617130925666559</x:v>
+      </x:c>
+      <x:c r="Q36" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B37" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C37" s="176" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="D37" s="186" t="n">
+        <x:v>15815</x:v>
+      </x:c>
+      <x:c r="E37" s="179" t="n">
+        <x:f>D37/D36-1</x:f>
+        <x:v>0.0904640419223608</x:v>
+      </x:c>
+      <x:c r="F37" s="187" t="n">
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="G37" s="179" t="n">
+        <x:f>F37/F36-1</x:f>
+        <x:v>0.10344827586206895</x:v>
+      </x:c>
+      <x:c r="H37" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I37" s="185" t="n">
+        <x:f>F37/H37</x:f>
+        <x:v>0.21050740765403975</x:v>
+      </x:c>
+      <x:c r="J37" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K37" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L37" s="188" t="n">
+        <x:v>1.562045</x:v>
+      </x:c>
+      <x:c r="M37" s="185" t="n">
+        <x:f>L37*K37*(0.6+0.4*F37/N37)</x:f>
+        <x:v>1.330280115559939</x:v>
+      </x:c>
+      <x:c r="N37" s="189" t="n">
+        <x:v>1848.362</x:v>
+      </x:c>
+      <x:c r="O37" s="189" t="n">
+        <x:v>1.562045</x:v>
+      </x:c>
+      <x:c r="P37" s="179" t="n">
+        <x:f>M37/O37-1</x:f>
+        <x:v>-0.14837273218125013</x:v>
+      </x:c>
+      <x:c r="Q37" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B38" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C38" s="176" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="D38" s="186" t="n">
+        <x:v>17236</x:v>
+      </x:c>
+      <x:c r="E38" s="179" t="n">
+        <x:f>D38/D37-1</x:f>
+        <x:v>0.08985140689219095</x:v>
+      </x:c>
+      <x:c r="F38" s="187" t="n">
+        <x:v>1850</x:v>
+      </x:c>
+      <x:c r="G38" s="179" t="n">
+        <x:f>F38/F37-1</x:f>
+        <x:v>0.15625</x:v>
+      </x:c>
+      <x:c r="H38" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I38" s="185" t="n">
+        <x:f>F38/H38</x:f>
+        <x:v>0.24339919009998345</x:v>
+      </x:c>
+      <x:c r="J38" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K38" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L38" s="188" t="n">
+        <x:v>1.50949</x:v>
+      </x:c>
+      <x:c r="M38" s="185" t="n">
+        <x:f>L38*K38*(0.6+0.4*F38/N38)</x:f>
+        <x:v>1.2857568345426678</x:v>
+      </x:c>
+      <x:c r="N38" s="189" t="n">
+        <x:v>2136.106</x:v>
+      </x:c>
+      <x:c r="O38" s="189" t="n">
+        <x:v>1.50949</x:v>
+      </x:c>
+      <x:c r="P38" s="179" t="n">
+        <x:f>M38/O38-1</x:f>
+        <x:v>-0.14821771953264495</x:v>
+      </x:c>
+      <x:c r="Q38" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B39" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C39" s="176" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="D39" s="186" t="n">
+        <x:v>18336</x:v>
+      </x:c>
+      <x:c r="E39" s="179" t="n">
+        <x:f>D39/D38-1</x:f>
+        <x:v>0.06381991181248559</x:v>
+      </x:c>
+      <x:c r="F39" s="187" t="n">
+        <x:v>1880</x:v>
+      </x:c>
+      <x:c r="G39" s="179" t="n">
+        <x:f>F39/F38-1</x:f>
+        <x:v>0.016216216216216273</x:v>
+      </x:c>
+      <x:c r="H39" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I39" s="185" t="n">
+        <x:f>F39/H39</x:f>
+        <x:v>0.2473462039934967</x:v>
+      </x:c>
+      <x:c r="J39" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+      <x:c r="K39" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="L39" s="188" t="n">
+        <x:v>1.489165</x:v>
+      </x:c>
+      <x:c r="M39" s="185" t="n">
+        <x:f>L39*K39*(0.6+0.4*F39/N39)</x:f>
+        <x:v>1.2713682236537283</x:v>
+      </x:c>
+      <x:c r="N39" s="189" t="n">
+        <x:v>2157.161</x:v>
+      </x:c>
+      <x:c r="O39" s="189" t="n">
+        <x:v>1.489165</x:v>
+      </x:c>
+      <x:c r="P39" s="179" t="n">
+        <x:f>M39/O39-1</x:f>
+        <x:v>-0.1462542944175238</x:v>
+      </x:c>
+      <x:c r="Q39" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B40" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C40" s="176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D40" s="186" t="n">
+        <x:v>11206</x:v>
+      </x:c>
+      <x:c r="E40" s="179"/>
+      <x:c r="F40" s="187" t="n">
+        <x:v>950</x:v>
+      </x:c>
+      <x:c r="G40" s="179"/>
+      <x:c r="H40" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I40" s="185" t="n">
+        <x:f>F40/H40</x:f>
+        <x:v>0.1249887732945861</x:v>
+      </x:c>
+      <x:c r="J40" s="176" t="str">
+        <x:v>旧PE曲线×新旧利润比</x:v>
+      </x:c>
+      <x:c r="K40" s="188"/>
+      <x:c r="L40" s="188" t="n">
+        <x:v>7.982385</x:v>
+      </x:c>
+      <x:c r="M40" s="185" t="n">
+        <x:f>L40*F40/N40</x:f>
+        <x:v>6.228191826185085</x:v>
+      </x:c>
+      <x:c r="N40" s="189" t="n">
+        <x:v>1217.571</x:v>
+      </x:c>
+      <x:c r="O40" s="189" t="n">
+        <x:v>7.982385</x:v>
+      </x:c>
+      <x:c r="P40" s="179" t="n">
+        <x:f>M40/O40-1</x:f>
+        <x:v>-0.21975802643131281</x:v>
+      </x:c>
+      <x:c r="Q40" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B41" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C41" s="176" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="D41" s="186" t="n">
+        <x:v>15420</x:v>
+      </x:c>
+      <x:c r="E41" s="179" t="n">
+        <x:f>D41/D40-1</x:f>
+        <x:v>0.3760485454220952</x:v>
+      </x:c>
+      <x:c r="F41" s="187" t="n">
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="G41" s="179" t="n">
+        <x:f>F41/F40-1</x:f>
+        <x:v>0.6842105263157894</x:v>
+      </x:c>
+      <x:c r="H41" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I41" s="185" t="n">
+        <x:f>F41/H41</x:f>
+        <x:v>0.21050740765403975</x:v>
+      </x:c>
+      <x:c r="J41" s="176" t="str">
+        <x:v>旧PE曲线×新旧利润比</x:v>
+      </x:c>
+      <x:c r="K41" s="188"/>
+      <x:c r="L41" s="188" t="n">
+        <x:v>6.163171</x:v>
+      </x:c>
+      <x:c r="M41" s="185" t="n">
+        <x:f>L41*F41/N41</x:f>
+        <x:v>5.2447916007371695</x:v>
+      </x:c>
+      <x:c r="N41" s="189" t="n">
+        <x:v>1880.165</x:v>
+      </x:c>
+      <x:c r="O41" s="189" t="n">
+        <x:v>6.163171</x:v>
+      </x:c>
+      <x:c r="P41" s="179" t="n">
+        <x:f>M41/O41-1</x:f>
+        <x:v>-0.1490108580895826</x:v>
+      </x:c>
+      <x:c r="Q41" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B42" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C42" s="176" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="D42" s="186" t="n">
+        <x:v>17382</x:v>
+      </x:c>
+      <x:c r="E42" s="179" t="n">
+        <x:f>D42/D41-1</x:f>
+        <x:v>0.1272373540856031</x:v>
+      </x:c>
+      <x:c r="F42" s="187" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="G42" s="179" t="n">
+        <x:f>F42/F41-1</x:f>
+        <x:v>0.125</x:v>
+      </x:c>
+      <x:c r="H42" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I42" s="185" t="n">
+        <x:f>F42/H42</x:f>
+        <x:v>0.2368208336107947</x:v>
+      </x:c>
+      <x:c r="J42" s="176" t="str">
+        <x:v>旧PE曲线×新旧利润比</x:v>
+      </x:c>
+      <x:c r="K42" s="188"/>
+      <x:c r="L42" s="188" t="n">
+        <x:v>4.493228</x:v>
+      </x:c>
+      <x:c r="M42" s="185" t="n">
+        <x:f>L42*F42/N42</x:f>
+        <x:v>3.933593471482481</x:v>
+      </x:c>
+      <x:c r="N42" s="189" t="n">
+        <x:v>2056.087</x:v>
+      </x:c>
+      <x:c r="O42" s="189" t="n">
+        <x:v>4.493228</x:v>
+      </x:c>
+      <x:c r="P42" s="179" t="n">
+        <x:f>M42/O42-1</x:f>
+        <x:v>-0.1245506634690069</x:v>
+      </x:c>
+      <x:c r="Q42" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B43" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C43" s="176" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="D43" s="186" t="n">
+        <x:v>19916</x:v>
+      </x:c>
+      <x:c r="E43" s="179" t="n">
+        <x:f>D43/D42-1</x:f>
+        <x:v>0.14578299390173743</x:v>
+      </x:c>
+      <x:c r="F43" s="187" t="n">
+        <x:v>2250</x:v>
+      </x:c>
+      <x:c r="G43" s="179" t="n">
+        <x:f>F43/F42-1</x:f>
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="H43" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I43" s="185" t="n">
+        <x:f>F43/H43</x:f>
+        <x:v>0.29602604201349336</x:v>
+      </x:c>
+      <x:c r="J43" s="176" t="str">
+        <x:v>旧PE曲线×新旧利润比</x:v>
+      </x:c>
+      <x:c r="K43" s="188"/>
+      <x:c r="L43" s="188" t="n">
+        <x:v>5.419324</x:v>
+      </x:c>
+      <x:c r="M43" s="185" t="n">
+        <x:f>L43*F43/N43</x:f>
+        <x:v>4.678691322487034</x:v>
+      </x:c>
+      <x:c r="N43" s="189" t="n">
+        <x:v>2606.173</x:v>
+      </x:c>
+      <x:c r="O43" s="189" t="n">
+        <x:v>5.419324</x:v>
+      </x:c>
+      <x:c r="P43" s="179" t="n">
+        <x:f>M43/O43-1</x:f>
+        <x:v>-0.13666514080224135</x:v>
+      </x:c>
+      <x:c r="Q43" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B44" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C44" s="176" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="D44" s="186" t="n">
+        <x:v>22160</x:v>
+      </x:c>
+      <x:c r="E44" s="179" t="n">
+        <x:f>D44/D43-1</x:f>
+        <x:v>0.11267322755573406</x:v>
+      </x:c>
+      <x:c r="F44" s="187" t="n">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="G44" s="179" t="n">
+        <x:f>F44/F43-1</x:f>
+        <x:v>0.06666666666666665</x:v>
+      </x:c>
+      <x:c r="H44" s="178" t="n">
+        <x:v>7600.682645</x:v>
+      </x:c>
+      <x:c r="I44" s="185" t="n">
+        <x:f>F44/H44</x:f>
+        <x:v>0.3157611114810596</x:v>
+      </x:c>
+      <x:c r="J44" s="176" t="str">
+        <x:v>旧PE曲线×新旧利润比</x:v>
+      </x:c>
+      <x:c r="K44" s="188"/>
+      <x:c r="L44" s="188" t="n">
+        <x:v>5.508804</x:v>
+      </x:c>
+      <x:c r="M44" s="185" t="n">
+        <x:f>L44*F44/N44</x:f>
+        <x:v>4.7364167805291855</x:v>
+      </x:c>
+      <x:c r="N44" s="189" t="n">
+        <x:v>2791.378</x:v>
+      </x:c>
+      <x:c r="O44" s="189" t="n">
+        <x:v>5.508804</x:v>
+      </x:c>
+      <x:c r="P44" s="179" t="n">
+        <x:f>M44/O44-1</x:f>
+        <x:v>-0.1402096025690539</x:v>
+      </x:c>
+      <x:c r="Q44" s="181" t="str">
+        <x:v>H1矿山成本和权益利润弱于旧模型；标准情景对旧SOTP施加10%成本折价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B45" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C45" s="176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D45" s="186" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="E45" s="179"/>
+      <x:c r="F45" s="187" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G45" s="179"/>
+      <x:c r="H45" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I45" s="185" t="n">
+        <x:f>F45/H45</x:f>
+        <x:v>0.08177144624013541</x:v>
+      </x:c>
+      <x:c r="J45" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K45" s="188" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L45" s="188" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="M45" s="185" t="n">
+        <x:f>F45/H45*K45+L45</x:f>
+        <x:v>1.5906286774408125</x:v>
+      </x:c>
+      <x:c r="N45" s="189" t="n">
+        <x:v>90.9</x:v>
+      </x:c>
+      <x:c r="O45" s="189" t="n">
+        <x:v>2.4216</x:v>
+      </x:c>
+      <x:c r="P45" s="179" t="n">
+        <x:f>M45/O45-1</x:f>
+        <x:v>-0.34314970373273357</x:v>
+      </x:c>
+      <x:c r="Q45" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B46" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C46" s="176" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="D46" s="186" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="E46" s="179" t="n">
+        <x:f>D46/D45-1</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F46" s="187" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G46" s="179" t="n">
+        <x:f>F46/F45-1</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H46" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I46" s="185" t="n">
+        <x:f>F46/H46</x:f>
+        <x:v>0.12265716936020311</x:v>
+      </x:c>
+      <x:c r="J46" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K46" s="188" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L46" s="188" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="M46" s="185" t="n">
+        <x:f>F46/H46*K46+L46</x:f>
+        <x:v>1.7859430161612186</x:v>
+      </x:c>
+      <x:c r="N46" s="189" t="n">
+        <x:v>108.2</x:v>
+      </x:c>
+      <x:c r="O46" s="189" t="n">
+        <x:v>2.3088</x:v>
+      </x:c>
+      <x:c r="P46" s="179" t="n">
+        <x:f>M46/O46-1</x:f>
+        <x:v>-0.2264626575878298</x:v>
+      </x:c>
+      <x:c r="Q46" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B47" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C47" s="176" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="D47" s="186" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="E47" s="179" t="n">
+        <x:f>D47/D46-1</x:f>
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="F47" s="187" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G47" s="179" t="n">
+        <x:f>F47/F46-1</x:f>
+        <x:v>0.16666666666666674</x:v>
+      </x:c>
+      <x:c r="H47" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I47" s="185" t="n">
+        <x:f>F47/H47</x:f>
+        <x:v>0.14310003092023696</x:v>
+      </x:c>
+      <x:c r="J47" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K47" s="188" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L47" s="188" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M47" s="185" t="n">
+        <x:f>F47/H47*K47+L47</x:f>
+        <x:v>1.8586001855214218</x:v>
+      </x:c>
+      <x:c r="N47" s="189" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="O47" s="189" t="n">
+        <x:v>2.24</x:v>
+      </x:c>
+      <x:c r="P47" s="179" t="n">
+        <x:f>M47/O47-1</x:f>
+        <x:v>-0.17026777432079387</x:v>
+      </x:c>
+      <x:c r="Q47" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B48" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C48" s="176" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="D48" s="186" t="n">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="E48" s="179" t="n">
+        <x:f>D48/D47-1</x:f>
+        <x:v>0.1333333333333333</x:v>
+      </x:c>
+      <x:c r="F48" s="187" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G48" s="179" t="n">
+        <x:f>F48/F47-1</x:f>
+        <x:v>0.0714285714285714</x:v>
+      </x:c>
+      <x:c r="H48" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I48" s="185" t="n">
+        <x:f>F48/H48</x:f>
+        <x:v>0.15332146170025387</x:v>
+      </x:c>
+      <x:c r="J48" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K48" s="188" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L48" s="188" t="n">
+        <x:v>0.95</x:v>
+      </x:c>
+      <x:c r="M48" s="185" t="n">
+        <x:f>F48/H48*K48+L48</x:f>
+        <x:v>1.8699287702015233</x:v>
+      </x:c>
+      <x:c r="N48" s="189" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="O48" s="189" t="n">
+        <x:v>2.18</x:v>
+      </x:c>
+      <x:c r="P48" s="179" t="n">
+        <x:f>M48/O48-1</x:f>
+        <x:v>-0.14223450908187008</x:v>
+      </x:c>
+      <x:c r="Q48" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B49" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C49" s="176" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="D49" s="186" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="E49" s="179" t="n">
+        <x:f>D49/D48-1</x:f>
+        <x:v>0.05882352941176472</x:v>
+      </x:c>
+      <x:c r="F49" s="187" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G49" s="179" t="n">
+        <x:f>F49/F48-1</x:f>
+        <x:v>0.06666666666666665</x:v>
+      </x:c>
+      <x:c r="H49" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I49" s="185" t="n">
+        <x:f>F49/H49</x:f>
+        <x:v>0.16354289248027082</x:v>
+      </x:c>
+      <x:c r="J49" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K49" s="188" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L49" s="188" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="M49" s="185" t="n">
+        <x:f>F49/H49*K49+L49</x:f>
+        <x:v>1.881257354881625</x:v>
+      </x:c>
+      <x:c r="N49" s="189" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="O49" s="189" t="n">
+        <x:v>2.1376</x:v>
+      </x:c>
+      <x:c r="P49" s="179" t="n">
+        <x:f>M49/O49-1</x:f>
+        <x:v>-0.11992077335253326</x:v>
+      </x:c>
+      <x:c r="Q49" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B50" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C50" s="176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D50" s="186" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="E50" s="179"/>
+      <x:c r="F50" s="187" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="G50" s="179"/>
+      <x:c r="H50" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I50" s="185" t="n">
+        <x:f>F50/H50</x:f>
+        <x:v>0.18398575404030465</x:v>
+      </x:c>
+      <x:c r="J50" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K50" s="188" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L50" s="188" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="M50" s="185" t="n">
+        <x:f>F50/H50*K50+L50</x:f>
+        <x:v>2.671886032322437</x:v>
+      </x:c>
+      <x:c r="N50" s="189" t="n">
+        <x:v>119.2</x:v>
+      </x:c>
+      <x:c r="O50" s="189" t="n">
+        <x:v>3.9072</x:v>
+      </x:c>
+      <x:c r="P50" s="179" t="n">
+        <x:f>M50/O50-1</x:f>
+        <x:v>-0.316163484765961</x:v>
+      </x:c>
+      <x:c r="Q50" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B51" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C51" s="176" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="D51" s="186" t="n">
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="E51" s="179" t="n">
+        <x:f>D51/D50-1</x:f>
+        <x:v>0.46666666666666656</x:v>
+      </x:c>
+      <x:c r="F51" s="187" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G51" s="179" t="n">
+        <x:f>F51/F50-1</x:f>
+        <x:v>0.5555555555555556</x:v>
+      </x:c>
+      <x:c r="H51" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I51" s="185" t="n">
+        <x:f>F51/H51</x:f>
+        <x:v>0.2862000618404739</x:v>
+      </x:c>
+      <x:c r="J51" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K51" s="188" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L51" s="188" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="M51" s="185" t="n">
+        <x:f>F51/H51*K51+L51</x:f>
+        <x:v>3.5896004947237916</x:v>
+      </x:c>
+      <x:c r="N51" s="189" t="n">
+        <x:v>153.1</x:v>
+      </x:c>
+      <x:c r="O51" s="189" t="n">
+        <x:v>4.504</x:v>
+      </x:c>
+      <x:c r="P51" s="179" t="n">
+        <x:f>M51/O51-1</x:f>
+        <x:v>-0.20301942834729303</x:v>
+      </x:c>
+      <x:c r="Q51" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B52" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C52" s="176" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="D52" s="186" t="n">
+        <x:v>2700</x:v>
+      </x:c>
+      <x:c r="E52" s="179" t="n">
+        <x:f>D52/D51-1</x:f>
+        <x:v>0.2272727272727273</x:v>
+      </x:c>
+      <x:c r="F52" s="187" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="G52" s="179" t="n">
+        <x:f>F52/F51-1</x:f>
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="H52" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I52" s="185" t="n">
+        <x:f>F52/H52</x:f>
+        <x:v>0.3577500773005924</x:v>
+      </x:c>
+      <x:c r="J52" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K52" s="188" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L52" s="188" t="n">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="M52" s="185" t="n">
+        <x:f>F52/H52*K52+L52</x:f>
+        <x:v>4.312000618404739</x:v>
+      </x:c>
+      <x:c r="N52" s="189" t="n">
+        <x:v>185.4</x:v>
+      </x:c>
+      <x:c r="O52" s="189" t="n">
+        <x:v>4.944</x:v>
+      </x:c>
+      <x:c r="P52" s="179" t="n">
+        <x:f>M52/O52-1</x:f>
+        <x:v>-0.1278315901284912</x:v>
+      </x:c>
+      <x:c r="Q52" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B53" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C53" s="176" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="D53" s="186" t="n">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="E53" s="179" t="n">
+        <x:f>D53/D52-1</x:f>
+        <x:v>0.14814814814814814</x:v>
+      </x:c>
+      <x:c r="F53" s="187" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G53" s="179" t="n">
+        <x:f>F53/F52-1</x:f>
+        <x:v>0.17142857142857149</x:v>
+      </x:c>
+      <x:c r="H53" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I53" s="185" t="n">
+        <x:f>F53/H53</x:f>
+        <x:v>0.41907866198069393</x:v>
+      </x:c>
+      <x:c r="J53" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K53" s="188" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L53" s="188" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="M53" s="185" t="n">
+        <x:f>F53/H53*K53+L53</x:f>
+        <x:v>4.952629295845552</x:v>
+      </x:c>
+      <x:c r="N53" s="189" t="n">
+        <x:v>224.7</x:v>
+      </x:c>
+      <x:c r="O53" s="189" t="n">
+        <x:v>5.344</x:v>
+      </x:c>
+      <x:c r="P53" s="179" t="n">
+        <x:f>M53/O53-1</x:f>
+        <x:v>-0.07323553595704502</x:v>
+      </x:c>
+      <x:c r="Q53" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B54" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C54" s="176" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="D54" s="186" t="n">
+        <x:v>3400</x:v>
+      </x:c>
+      <x:c r="E54" s="179" t="n">
+        <x:f>D54/D53-1</x:f>
+        <x:v>0.09677419354838701</x:v>
+      </x:c>
+      <x:c r="F54" s="187" t="n">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G54" s="179" t="n">
+        <x:f>F54/F53-1</x:f>
+        <x:v>0.09756097560975618</x:v>
+      </x:c>
+      <x:c r="H54" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I54" s="185" t="n">
+        <x:f>F54/H54</x:f>
+        <x:v>0.45996438510076165</x:v>
+      </x:c>
+      <x:c r="J54" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K54" s="188" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L54" s="188" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="M54" s="185" t="n">
+        <x:f>F54/H54*K54+L54</x:f>
+        <x:v>5.429715080806093</x:v>
+      </x:c>
+      <x:c r="N54" s="189" t="n">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="O54" s="189" t="n">
+        <x:v>5.8768</x:v>
+      </x:c>
+      <x:c r="P54" s="179" t="n">
+        <x:f>M54/O54-1</x:f>
+        <x:v>-0.07607625224508352</x:v>
+      </x:c>
+      <x:c r="Q54" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B55" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C55" s="176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D55" s="186" t="n">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="E55" s="179"/>
+      <x:c r="F55" s="187" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G55" s="179"/>
+      <x:c r="H55" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I55" s="185" t="n">
+        <x:f>F55/H55</x:f>
+        <x:v>0.2862000618404739</x:v>
+      </x:c>
+      <x:c r="J55" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K55" s="188" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L55" s="188" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="M55" s="185" t="n">
+        <x:f>F55/H55*K55+L55</x:f>
+        <x:v>3.5396004947237913</x:v>
+      </x:c>
+      <x:c r="N55" s="189" t="n">
+        <x:v>149.6</x:v>
+      </x:c>
+      <x:c r="O55" s="189" t="n">
+        <x:v>4.9472</x:v>
+      </x:c>
+      <x:c r="P55" s="179" t="n">
+        <x:f>M55/O55-1</x:f>
+        <x:v>-0.28452447955938887</x:v>
+      </x:c>
+      <x:c r="Q55" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B56" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C56" s="176" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="D56" s="186" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="E56" s="179" t="n">
+        <x:f>D56/D55-1</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F56" s="187" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G56" s="179" t="n">
+        <x:f>F56/F55-1</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H56" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I56" s="185" t="n">
+        <x:f>F56/H56</x:f>
+        <x:v>0.4293000927607109</x:v>
+      </x:c>
+      <x:c r="J56" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K56" s="188" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L56" s="188" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="M56" s="185" t="n">
+        <x:f>F56/H56*K56+L56</x:f>
+        <x:v>4.684400742085687</x:v>
+      </x:c>
+      <x:c r="N56" s="189" t="n">
+        <x:v>224.2</x:v>
+      </x:c>
+      <x:c r="O56" s="189" t="n">
+        <x:v>5.7576</x:v>
+      </x:c>
+      <x:c r="P56" s="179" t="n">
+        <x:f>M56/O56-1</x:f>
+        <x:v>-0.18639698101888158</x:v>
+      </x:c>
+      <x:c r="Q56" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B57" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C57" s="176" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="D57" s="186" t="n">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="E57" s="179" t="n">
+        <x:f>D57/D56-1</x:f>
+        <x:v>0.33333333333333326</x:v>
+      </x:c>
+      <x:c r="F57" s="187" t="n">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="G57" s="179" t="n">
+        <x:f>F57/F56-1</x:f>
+        <x:v>0.33333333333333326</x:v>
+      </x:c>
+      <x:c r="H57" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I57" s="185" t="n">
+        <x:f>F57/H57</x:f>
+        <x:v>0.5724001236809478</x:v>
+      </x:c>
+      <x:c r="J57" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K57" s="188" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L57" s="188" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="M57" s="185" t="n">
+        <x:f>F57/H57*K57+L57</x:f>
+        <x:v>5.779200989447583</x:v>
+      </x:c>
+      <x:c r="N57" s="189" t="n">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="O57" s="189" t="n">
+        <x:v>6.4512</x:v>
+      </x:c>
+      <x:c r="P57" s="179" t="n">
+        <x:f>M57/O57-1</x:f>
+        <x:v>-0.1041665132924754</x:v>
+      </x:c>
+      <x:c r="Q57" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B58" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C58" s="176" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="D58" s="186" t="n">
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="E58" s="179" t="n">
+        <x:f>D58/D57-1</x:f>
+        <x:v>0.19999999999999996</x:v>
+      </x:c>
+      <x:c r="F58" s="187" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="G58" s="179" t="n">
+        <x:f>F58/F57-1</x:f>
+        <x:v>0.1785714285714286</x:v>
+      </x:c>
+      <x:c r="H58" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I58" s="185" t="n">
+        <x:f>F58/H58</x:f>
+        <x:v>0.6746144314811171</x:v>
+      </x:c>
+      <x:c r="J58" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K58" s="188" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L58" s="188" t="n">
+        <x:v>1.15</x:v>
+      </x:c>
+      <x:c r="M58" s="185" t="n">
+        <x:f>F58/H58*K58+L58</x:f>
+        <x:v>6.546915451848937</x:v>
+      </x:c>
+      <x:c r="N58" s="189" t="n">
+        <x:v>409.5</x:v>
+      </x:c>
+      <x:c r="O58" s="189" t="n">
+        <x:v>6.984</x:v>
+      </x:c>
+      <x:c r="P58" s="179" t="n">
+        <x:f>M58/O58-1</x:f>
+        <x:v>-0.06258369818886922</x:v>
+      </x:c>
+      <x:c r="Q58" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B59" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C59" s="176" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="D59" s="186" t="n">
+        <x:v>5400</x:v>
+      </x:c>
+      <x:c r="E59" s="179" t="n">
+        <x:f>D59/D58-1</x:f>
+        <x:v>0.125</x:v>
+      </x:c>
+      <x:c r="F59" s="187" t="n">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="G59" s="179" t="n">
+        <x:f>F59/F58-1</x:f>
+        <x:v>0.10606060606060597</x:v>
+      </x:c>
+      <x:c r="H59" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I59" s="185" t="n">
+        <x:f>F59/H59</x:f>
+        <x:v>0.7461644469412356</x:v>
+      </x:c>
+      <x:c r="J59" s="176" t="str">
+        <x:v>PE+可分配净现金</x:v>
+      </x:c>
+      <x:c r="K59" s="188" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L59" s="188" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="M59" s="185" t="n">
+        <x:f>F59/H59*K59+L59</x:f>
+        <x:v>7.069315575529885</x:v>
+      </x:c>
+      <x:c r="N59" s="189" t="n">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="O59" s="189" t="n">
+        <x:v>7.5576</x:v>
+      </x:c>
+      <x:c r="P59" s="179" t="n">
+        <x:f>M59/O59-1</x:f>
+        <x:v>-0.06460839743703228</x:v>
+      </x:c>
+      <x:c r="Q59" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B60" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C60" s="176" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="D60" s="186" t="n">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="E60" s="179"/>
+      <x:c r="F60" s="187" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G60" s="179"/>
+      <x:c r="H60" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I60" s="185" t="n">
+        <x:f>F60/H60</x:f>
+        <x:v>0.32708578496054164</x:v>
+      </x:c>
+      <x:c r="J60" s="176" t="str">
+        <x:v>Super Bull PE曲线</x:v>
+      </x:c>
+      <x:c r="K60" s="188" t="n">
+        <x:v>10.9336923</x:v>
+      </x:c>
+      <x:c r="L60" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M60" s="185" t="n">
+        <x:f>F60/H60*K60+L60</x:f>
+        <x:v>3.5762553284625302</x:v>
+      </x:c>
+      <x:c r="N60" s="189" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="O60" s="189" t="n">
+        <x:v>3.577</x:v>
+      </x:c>
+      <x:c r="P60" s="179" t="n">
+        <x:f>M60/O60-1</x:f>
+        <x:v>-0.00020818326459870473</x:v>
+      </x:c>
+      <x:c r="Q60" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B61" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C61" s="176" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="D61" s="186" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="E61" s="179" t="n">
+        <x:f>D61/D60-1</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="F61" s="187" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G61" s="179" t="n">
+        <x:f>F61/F60-1</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H61" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I61" s="185" t="n">
+        <x:f>F61/H61</x:f>
+        <x:v>0.49062867744081246</x:v>
+      </x:c>
+      <x:c r="J61" s="176" t="str">
+        <x:v>Super Bull PE曲线</x:v>
+      </x:c>
+      <x:c r="K61" s="188" t="n">
+        <x:v>5.46684615</x:v>
+      </x:c>
+      <x:c r="L61" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M61" s="185" t="n">
+        <x:f>F61/H61*K61+L61</x:f>
+        <x:v>2.6821914963468974</x:v>
+      </x:c>
+      <x:c r="N61" s="189" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="O61" s="189" t="n">
+        <x:v>2.682</x:v>
+      </x:c>
+      <x:c r="P61" s="179" t="n">
+        <x:f>M61/O61-1</x:f>
+        <x:v>0.0000714005767701309</x:v>
+      </x:c>
+      <x:c r="Q61" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B62" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C62" s="176" t="n">
+        <x:v>2028</x:v>
+      </x:c>
+      <x:c r="D62" s="186" t="n">
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="E62" s="179" t="n">
+        <x:f>D62/D61-1</x:f>
+        <x:v>0.33333333333333326</x:v>
+      </x:c>
+      <x:c r="F62" s="187" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="G62" s="179" t="n">
+        <x:f>F62/F61-1</x:f>
+        <x:v>0.33333333333333326</x:v>
+      </x:c>
+      <x:c r="H62" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I62" s="185" t="n">
+        <x:f>F62/H62</x:f>
+        <x:v>0.6541715699210833</x:v>
+      </x:c>
+      <x:c r="J62" s="176" t="str">
+        <x:v>Super Bull PE曲线</x:v>
+      </x:c>
+      <x:c r="K62" s="188" t="n">
+        <x:v>3.6445641</x:v>
+      </x:c>
+      <x:c r="L62" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M62" s="185" t="n">
+        <x:f>F62/H62*K62+L62</x:f>
+        <x:v>2.38417021897502</x:v>
+      </x:c>
+      <x:c r="N62" s="189" t="n">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="O62" s="189" t="n">
+        <x:v>2.384</x:v>
+      </x:c>
+      <x:c r="P62" s="179" t="n">
+        <x:f>M62/O62-1</x:f>
+        <x:v>0.0000714005767701309</x:v>
+      </x:c>
+      <x:c r="Q62" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B63" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C63" s="176" t="n">
+        <x:v>2029</x:v>
+      </x:c>
+      <x:c r="D63" s="186" t="n">
+        <x:v>5900</x:v>
+      </x:c>
+      <x:c r="E63" s="179" t="n">
+        <x:f>D63/D62-1</x:f>
+        <x:v>0.22916666666666674</x:v>
+      </x:c>
+      <x:c r="F63" s="187" t="n">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="G63" s="179" t="n">
+        <x:f>F63/F62-1</x:f>
+        <x:v>0.1875</x:v>
+      </x:c>
+      <x:c r="H63" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I63" s="185" t="n">
+        <x:f>F63/H63</x:f>
+        <x:v>0.7768287392812864</x:v>
+      </x:c>
+      <x:c r="J63" s="176" t="str">
+        <x:v>Super Bull PE曲线</x:v>
+      </x:c>
+      <x:c r="K63" s="188" t="n">
+        <x:v>9.32228205</x:v>
+      </x:c>
+      <x:c r="L63" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M63" s="185" t="n">
+        <x:f>F63/H63*K63+L63</x:f>
+        <x:v>7.241816612126066</x:v>
+      </x:c>
+      <x:c r="N63" s="189" t="n">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="O63" s="189" t="n">
+        <x:v>7.243</x:v>
+      </x:c>
+      <x:c r="P63" s="179" t="n">
+        <x:f>M63/O63-1</x:f>
+        <x:v>-0.00016338366339008203</x:v>
+      </x:c>
+      <x:c r="Q63" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B64" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C64" s="176" t="n">
+        <x:v>2030</x:v>
+      </x:c>
+      <x:c r="D64" s="186" t="n">
+        <x:v>6800</x:v>
+      </x:c>
+      <x:c r="E64" s="179" t="n">
+        <x:f>D64/D63-1</x:f>
+        <x:v>0.15254237288135597</x:v>
+      </x:c>
+      <x:c r="F64" s="187" t="n">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="G64" s="179" t="n">
+        <x:f>F64/F63-1</x:f>
+        <x:v>0.13157894736842102</x:v>
+      </x:c>
+      <x:c r="H64" s="178" t="n">
+        <x:v>489.168308</x:v>
+      </x:c>
+      <x:c r="I64" s="185" t="n">
+        <x:f>F64/H64</x:f>
+        <x:v>0.8790430470814556</x:v>
+      </x:c>
+      <x:c r="J64" s="176" t="str">
+        <x:v>Super Bull PE曲线</x:v>
+      </x:c>
+      <x:c r="K64" s="188" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L64" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M64" s="185" t="n">
+        <x:f>F64/H64*K64+L64</x:f>
+        <x:v>13.185645706221834</x:v>
+      </x:c>
+      <x:c r="N64" s="189" t="n">
+        <x:v>448.117</x:v>
+      </x:c>
+      <x:c r="O64" s="189" t="n">
+        <x:v>13.744</x:v>
+      </x:c>
+      <x:c r="P64" s="179" t="n">
+        <x:f>M64/O64-1</x:f>
+        <x:v>-0.04062531241110057</x:v>
+      </x:c>
+      <x:c r="Q64" s="181" t="str">
+        <x:v>H1交易量收缩；下调收入与利润，同时保留净现金/低风险关联交易缓冲</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:Q1"/>
+    <x:mergeCell ref="A2:Q2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="13" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="165" t="str">
+        <x:v>2030年末合理价、TSR与11%最大买价</x:v>
+      </x:c>
+      <x:c r="B1" s="165"/>
+      <x:c r="C1" s="165"/>
+      <x:c r="D1" s="165"/>
+      <x:c r="E1" s="165"/>
+      <x:c r="F1" s="165"/>
+      <x:c r="G1" s="165"/>
+      <x:c r="H1" s="165"/>
+      <x:c r="I1" s="165"/>
+      <x:c r="J1" s="165"/>
+      <x:c r="K1" s="165"/>
+      <x:c r="L1" s="165"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="169" t="str">
+        <x:v>当前价为2026-09-02未复权收盘价；合理价为模型在各年末给出的权益价值，不是市场价格预测。TSR包含模型累计股息，历史股价和未来合理价均不做红利再投资。</x:v>
+      </x:c>
+      <x:c r="B2" s="169"/>
+      <x:c r="C2" s="169"/>
+      <x:c r="D2" s="169"/>
+      <x:c r="E2" s="169"/>
+      <x:c r="F2" s="169"/>
+      <x:c r="G2" s="169"/>
+      <x:c r="H2" s="169"/>
+      <x:c r="I2" s="169"/>
+      <x:c r="J2" s="169"/>
+      <x:c r="K2" s="169"/>
+      <x:c r="L2" s="169"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="174" t="str">
+        <x:v>公司</x:v>
+      </x:c>
+      <x:c r="B4" s="174" t="str">
+        <x:v>情景</x:v>
+      </x:c>
+      <x:c r="C4" s="174" t="str">
+        <x:v>当前价</x:v>
+      </x:c>
+      <x:c r="D4" s="174" t="str">
+        <x:v>2030合理价</x:v>
+      </x:c>
+      <x:c r="E4" s="174" t="str">
+        <x:v>累计股息</x:v>
+      </x:c>
+      <x:c r="F4" s="174" t="str">
+        <x:v>持有年数</x:v>
+      </x:c>
+      <x:c r="G4" s="174" t="str">
+        <x:v>年化TSR</x:v>
+      </x:c>
+      <x:c r="H4" s="174" t="str">
+        <x:v>要求回报率</x:v>
+      </x:c>
+      <x:c r="I4" s="174" t="str">
+        <x:v>11%最大买价</x:v>
+      </x:c>
+      <x:c r="J4" s="174" t="str">
+        <x:v>是否通过</x:v>
+      </x:c>
+      <x:c r="K4" s="174" t="str">
+        <x:v>旧版2030合理价</x:v>
+      </x:c>
+      <x:c r="L4" s="174" t="str">
+        <x:v>合理价变化</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B5" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C5" s="188" t="n">
+        <x:v>66.42</x:v>
+      </x:c>
+      <x:c r="D5" s="185" t="n">
+        <x:f>'更新后预测'!M9</x:f>
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="E5" s="188" t="n">
+        <x:v>0.385</x:v>
+      </x:c>
+      <x:c r="F5" s="191" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="G5" s="179" t="n">
+        <x:f>((D5+E5)/C5)^(1/F5)-1</x:f>
+        <x:v>-0.4354941706767208</x:v>
+      </x:c>
+      <x:c r="H5" s="187" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="I5" s="185" t="n">
+        <x:f>D5/(1+H5)^F5+E5/(1+H5)^2.5</x:f>
+        <x:v>3.606030343120275</x:v>
+      </x:c>
+      <x:c r="J5" s="185" t="str">
+        <x:f>IF(I5&gt;=C5,"通过","不通过")</x:f>
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="K5" s="185" t="n">
+        <x:v>4.913</x:v>
+      </x:c>
+      <x:c r="L5" s="179" t="n">
+        <x:f>D5/K5-1</x:f>
+        <x:v>0.058416446163240376</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B6" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C6" s="188" t="n">
+        <x:v>66.42</x:v>
+      </x:c>
+      <x:c r="D6" s="185" t="n">
+        <x:f>'更新后预测'!M14</x:f>
+        <x:v>21.6</x:v>
+      </x:c>
+      <x:c r="E6" s="188" t="n">
+        <x:v>1.229</x:v>
+      </x:c>
+      <x:c r="F6" s="191" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="G6" s="179" t="n">
+        <x:f>((D6+E6)/C6)^(1/F6)-1</x:f>
+        <x:v>-0.21858081687046116</x:v>
+      </x:c>
+      <x:c r="H6" s="187" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="I6" s="185" t="n">
+        <x:f>D6/(1+H6)^F6+E6/(1+H6)^2.5</x:f>
+        <x:v>14.693685065360688</x:v>
+      </x:c>
+      <x:c r="J6" s="185" t="str">
+        <x:f>IF(I6&gt;=C6,"通过","不通过")</x:f>
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="K6" s="185" t="n">
+        <x:v>21.623</x:v>
+      </x:c>
+      <x:c r="L6" s="179" t="n">
+        <x:f>D6/K6-1</x:f>
+        <x:v>-0.0010636821902603177</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B7" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C7" s="188" t="n">
+        <x:v>66.42</x:v>
+      </x:c>
+      <x:c r="D7" s="185" t="n">
+        <x:f>'更新后预测'!M19</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E7" s="188" t="n">
+        <x:v>2.093</x:v>
+      </x:c>
+      <x:c r="F7" s="191" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="G7" s="179" t="n">
+        <x:f>((D7+E7)/C7)^(1/F7)-1</x:f>
+        <x:v>-0.15463060092506664</x:v>
+      </x:c>
+      <x:c r="H7" s="187" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="I7" s="185" t="n">
+        <x:f>D7/(1+H7)^F7+E7/(1+H7)^2.5</x:f>
+        <x:v>20.705296879684038</x:v>
+      </x:c>
+      <x:c r="J7" s="185" t="str">
+        <x:f>IF(I7&gt;=C7,"通过","不通过")</x:f>
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="K7" s="185" t="n">
+        <x:v>30.824</x:v>
+      </x:c>
+      <x:c r="L7" s="179" t="n">
+        <x:f>D7/K7-1</x:f>
+        <x:v>-0.026732416298987816</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="176" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="B8" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C8" s="188" t="n">
+        <x:v>66.42</x:v>
+      </x:c>
+      <x:c r="D8" s="185" t="n">
+        <x:f>'更新后预测'!M24</x:f>
+        <x:v>40.963</x:v>
+      </x:c>
+      <x:c r="E8" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="191" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="G8" s="179" t="n">
+        <x:f>((D8+E8)/C8)^(1/F8)-1</x:f>
+        <x:v>-0.10561891462797579</x:v>
+      </x:c>
+      <x:c r="H8" s="187" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="I8" s="185" t="n">
+        <x:f>D8/(1+H8)^F8+E8/(1+H8)^2.5</x:f>
+        <x:v>26.07013363352771</x:v>
+      </x:c>
+      <x:c r="J8" s="185" t="str">
+        <x:f>IF(I8&gt;=C8,"通过","不通过")</x:f>
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="K8" s="185" t="n">
+        <x:v>40.963</x:v>
+      </x:c>
+      <x:c r="L8" s="179" t="n">
+        <x:f>D8/K8-1</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B9" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C9" s="188" t="n">
+        <x:v>2.43</x:v>
+      </x:c>
+      <x:c r="D9" s="185" t="n">
+        <x:f>'更新后预测'!M29</x:f>
+        <x:v>0.44565240234284165</x:v>
+      </x:c>
+      <x:c r="E9" s="188" t="n">
+        <x:v>0.074</x:v>
+      </x:c>
+      <x:c r="F9" s="191" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="G9" s="179" t="n">
+        <x:f>((D9+E9)/C9)^(1/F9)-1</x:f>
+        <x:v>-0.2996901690129583</x:v>
+      </x:c>
+      <x:c r="H9" s="187" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="I9" s="185" t="n">
+        <x:f>D9/(1+H9)^F9+E9/(1+H9)^2.5</x:f>
+        <x:v>0.3406336054165128</x:v>
+      </x:c>
+      <x:c r="J9" s="185" t="str">
+        <x:f>IF(I9&gt;=C9,"通过","不通过")</x:f>
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="K9" s="185" t="n">
+        <x:v>0.538715</x:v>
+      </x:c>
+      <x:c r="L9" s="179" t="n">
+        <x:f>D9/K9-1</x:f>
+        <x:v>-0.17274922297904904</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B10" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C10" s="188" t="n">
+        <x:v>2.43</x:v>
+      </x:c>
+      <x:c r="D10" s="185" t="n">
+        <x:f>'更新后预测'!M34</x:f>
+        <x:v>0.8742132692656102</x:v>
+      </x:c>
+      <x:c r="E10" s="188" t="n">
+        <x:v>0.184</x:v>
+      </x:c>
+      <x:c r="F10" s="191" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="G10" s="179" t="n">
+        <x:f>((D10+E10)/C10)^(1/F10)-1</x:f>
+        <x:v>-0.1746834805982519</x:v>
+      </x:c>
+      <x:c r="H10" s="187" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="I10" s="185" t="n">
+        <x:f>D10/(1+H10)^F10+E10/(1+H10)^2.5</x:f>
+        <x:v>0.6981225086330841</x:v>
+      </x:c>
+      <x:c r="J10" s="185" t="str">
+        <x:f>IF(I10&gt;=C10,"通过","不通过")</x:f>
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="K10" s="185" t="n">
+        <x:v>1.009463</x:v>
+      </x:c>
+      <x:c r="L10" s="179" t="n">
+        <x:f>D10/K10-1</x:f>
+        <x:v>-0.13398186038952375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B11" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C11" s="188" t="n">
+        <x:v>2.43</x:v>
+      </x:c>
+      <x:c r="D11" s="185" t="n">
+        <x:f>'更新后预测'!M39</x:f>
+        <x:v>1.2713682236537283</x:v>
+      </x:c>
+      <x:c r="E11" s="188" t="n">
+        <x:v>0.353</x:v>
+      </x:c>
+      <x:c r="F11" s="191" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="G11" s="179" t="n">
+        <x:f>((D11+E11)/C11)^(1/F11)-1</x:f>
+        <x:v>-0.08882381907839298</x:v>
+      </x:c>
+      <x:c r="H11" s="187" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="I11" s="185" t="n">
+        <x:f>D11/(1+H11)^F11+E11/(1+H11)^2.5</x:f>
+        <x:v>1.081074824818029</x:v>
+      </x:c>
+      <x:c r="J11" s="185" t="str">
+        <x:f>IF(I11&gt;=C11,"通过","不通过")</x:f>
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="K11" s="185" t="n">
+        <x:v>1.489165</x:v>
+      </x:c>
+      <x:c r="L11" s="179" t="n">
+        <x:f>D11/K11-1</x:f>
+        <x:v>-0.1462542944175238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="176" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="B12" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C12" s="188" t="n">
+        <x:v>2.43</x:v>
+      </x:c>
+      <x:c r="D12" s="185" t="n">
+        <x:f>'更新后预测'!M44</x:f>
+        <x:v>4.7364167805291855</x:v>
+      </x:c>
+      <x:c r="E12" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="191" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="G12" s="179" t="n">
+        <x:f>((D12+E12)/C12)^(1/F12)-1</x:f>
+        <x:v>0.1666443561584834</x:v>
+      </x:c>
+      <x:c r="H12" s="187" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="I12" s="185" t="n">
+        <x:f>D12/(1+H12)^F12+E12/(1+H12)^2.5</x:f>
+        <x:v>3.0144036914405428</x:v>
+      </x:c>
+      <x:c r="J12" s="185" t="str">
+        <x:f>IF(I12&gt;=C12,"通过","不通过")</x:f>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="K12" s="185" t="n">
+        <x:v>5.508804</x:v>
+      </x:c>
+      <x:c r="L12" s="179" t="n">
+        <x:f>D12/K12-1</x:f>
+        <x:v>-0.1402096025690539</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B13" s="176" t="str">
+        <x:v>Bear</x:v>
+      </x:c>
+      <x:c r="C13" s="188" t="n">
+        <x:v>3.85</x:v>
+      </x:c>
+      <x:c r="D13" s="185" t="n">
+        <x:f>'更新后预测'!M49</x:f>
+        <x:v>1.881257354881625</x:v>
+      </x:c>
+      <x:c r="E13" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="191" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="G13" s="179" t="n">
+        <x:f>((D13+E13)/C13)^(1/F13)-1</x:f>
+        <x:v>-0.15243575299387058</x:v>
+      </x:c>
+      <x:c r="H13" s="187" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="I13" s="185" t="n">
+        <x:f>D13/(1+H13)^F13+E13/(1+H13)^2.5</x:f>
+        <x:v>1.1972909855435594</x:v>
+      </x:c>
+      <x:c r="J13" s="185" t="str">
+        <x:f>IF(I13&gt;=C13,"通过","不通过")</x:f>
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="K13" s="185" t="n">
+        <x:v>2.1376</x:v>
+      </x:c>
+      <x:c r="L13" s="179" t="n">
+        <x:f>D13/K13-1</x:f>
+        <x:v>-0.11992077335253326</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B14" s="176" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="C14" s="188" t="n">
+        <x:v>3.85</x:v>
+      </x:c>
+      <x:c r="D14" s="185" t="n">
+        <x:f>'更新后预测'!M54</x:f>
+        <x:v>5.429715080806093</x:v>
+      </x:c>
+      <x:c r="E14" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="191" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="G14" s="179" t="n">
+        <x:f>((D14+E14)/C14)^(1/F14)-1</x:f>
+        <x:v>0.08264016899666315</x:v>
+      </x:c>
+      <x:c r="H14" s="187" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="I14" s="185" t="n">
+        <x:f>D14/(1+H14)^F14+E14/(1+H14)^2.5</x:f>
+        <x:v>3.4556404010593846</x:v>
+      </x:c>
+      <x:c r="J14" s="185" t="str">
+        <x:f>IF(I14&gt;=C14,"通过","不通过")</x:f>
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="K14" s="185" t="n">
+        <x:v>5.8768</x:v>
+      </x:c>
+      <x:c r="L14" s="179" t="n">
+        <x:f>D14/K14-1</x:f>
+        <x:v>-0.07607625224508352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B15" s="176" t="str">
+        <x:v>Bull</x:v>
+      </x:c>
+      <x:c r="C15" s="188" t="n">
+        <x:v>3.85</x:v>
+      </x:c>
+      <x:c r="D15" s="185" t="n">
+        <x:f>'更新后预测'!M59</x:f>
+        <x:v>7.069315575529885</x:v>
+      </x:c>
+      <x:c r="E15" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="191" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="G15" s="179" t="n">
+        <x:f>((D15+E15)/C15)^(1/F15)-1</x:f>
+        <x:v>0.150669826872611</x:v>
+      </x:c>
+      <x:c r="H15" s="187" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="I15" s="185" t="n">
+        <x:f>D15/(1+H15)^F15+E15/(1+H15)^2.5</x:f>
+        <x:v>4.499133407017136</x:v>
+      </x:c>
+      <x:c r="J15" s="185" t="str">
+        <x:f>IF(I15&gt;=C15,"通过","不通过")</x:f>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="K15" s="185" t="n">
+        <x:v>7.5576</x:v>
+      </x:c>
+      <x:c r="L15" s="179" t="n">
+        <x:f>D15/K15-1</x:f>
+        <x:v>-0.06460839743703228</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="176" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="B16" s="176" t="str">
+        <x:v>Super Bull</x:v>
+      </x:c>
+      <x:c r="C16" s="188" t="n">
+        <x:v>3.85</x:v>
+      </x:c>
+      <x:c r="D16" s="185" t="n">
+        <x:f>'更新后预测'!M64</x:f>
+        <x:v>13.185645706221834</x:v>
+      </x:c>
+      <x:c r="E16" s="188" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="191" t="n">
+        <x:v>4.33</x:v>
+      </x:c>
+      <x:c r="G16" s="179" t="n">
+        <x:f>((D16+E16)/C16)^(1/F16)-1</x:f>
+        <x:v>0.3288427658461486</x:v>
+      </x:c>
+      <x:c r="H16" s="187" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="I16" s="185" t="n">
+        <x:f>D16/(1+H16)^F16+E16/(1+H16)^2.5</x:f>
+        <x:v>8.391757088239487</x:v>
+      </x:c>
+      <x:c r="J16" s="185" t="str">
+        <x:f>IF(I16&gt;=C16,"通过","不通过")</x:f>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="K16" s="185" t="n">
+        <x:v>13.744</x:v>
+      </x:c>
+      <x:c r="L16" s="179" t="n">
+        <x:f>D16/K16-1</x:f>
+        <x:v>-0.04062531241110057</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:L1"/>
+    <x:mergeCell ref="A2:L2"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="J5:J16">
+    <x:cfRule type="expression" dxfId="2" priority="1">
+      <x:formula>J5="通过"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="3" priority="2">
+      <x:formula>J5="不通过"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="3" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="165" t="str">
+        <x:v>历史股价与四情景年末合理价</x:v>
+      </x:c>
+      <x:c r="B1" s="165"/>
+      <x:c r="C1" s="165"/>
+      <x:c r="D1" s="165"/>
+      <x:c r="E1" s="165"/>
+      <x:c r="F1" s="165"/>
+      <x:c r="G1" s="165"/>
+      <x:c r="H1" s="165"/>
+      <x:c r="I1" s="165"/>
+      <x:c r="J1" s="165"/>
+      <x:c r="K1" s="165"/>
+      <x:c r="L1" s="165"/>
+      <x:c r="M1" s="165"/>
+      <x:c r="N1" s="165"/>
+      <x:c r="O1" s="165"/>
+      <x:c r="P1" s="165"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="169" t="str">
+        <x:v>历史：各自然年最后交易日未复权收盘价（不含股息）及2026-09-02收盘价。预测：2026E—2030E模型年末权益价值，不是市场价格预测。中国铀业2025-12-03上市，故更早历史为空。</x:v>
+      </x:c>
+      <x:c r="B2" s="169"/>
+      <x:c r="C2" s="169"/>
+      <x:c r="D2" s="169"/>
+      <x:c r="E2" s="169"/>
+      <x:c r="F2" s="169"/>
+      <x:c r="G2" s="169"/>
+      <x:c r="H2" s="169"/>
+      <x:c r="I2" s="169"/>
+      <x:c r="J2" s="169"/>
+      <x:c r="K2" s="169"/>
+      <x:c r="L2" s="169"/>
+      <x:c r="M2" s="169"/>
+      <x:c r="N2" s="169"/>
+      <x:c r="O2" s="169"/>
+      <x:c r="P2" s="169"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="174" t="str">
+        <x:v>期间</x:v>
+      </x:c>
+      <x:c r="B4" s="174" t="str">
+        <x:v>历史收盘价</x:v>
+      </x:c>
+      <x:c r="C4" s="174" t="str">
+        <x:v>Bear合理价</x:v>
+      </x:c>
+      <x:c r="D4" s="174" t="str">
+        <x:v>Base合理价</x:v>
+      </x:c>
+      <x:c r="E4" s="174" t="str">
+        <x:v>Bull合理价</x:v>
+      </x:c>
+      <x:c r="F4" s="174" t="str">
+        <x:v>Super Bull合理价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="176" t="str">
+        <x:v>2021A</x:v>
+      </x:c>
+      <x:c r="B5" s="185"/>
+      <x:c r="C5" s="185"/>
+      <x:c r="D5" s="185"/>
+      <x:c r="E5" s="185"/>
+      <x:c r="F5" s="185"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="176" t="str">
+        <x:v>2022A</x:v>
+      </x:c>
+      <x:c r="B6" s="185"/>
+      <x:c r="C6" s="185"/>
+      <x:c r="D6" s="185"/>
+      <x:c r="E6" s="185"/>
+      <x:c r="F6" s="185"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="176" t="str">
+        <x:v>2023A</x:v>
+      </x:c>
+      <x:c r="B7" s="185"/>
+      <x:c r="C7" s="185"/>
+      <x:c r="D7" s="185"/>
+      <x:c r="E7" s="185"/>
+      <x:c r="F7" s="185"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="176" t="str">
+        <x:v>2024A</x:v>
+      </x:c>
+      <x:c r="B8" s="185"/>
+      <x:c r="C8" s="185"/>
+      <x:c r="D8" s="185"/>
+      <x:c r="E8" s="185"/>
+      <x:c r="F8" s="185"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="176" t="str">
+        <x:v>2025A</x:v>
+      </x:c>
+      <x:c r="B9" s="185" t="n">
+        <x:v>60.92</x:v>
+      </x:c>
+      <x:c r="C9" s="185"/>
+      <x:c r="D9" s="185"/>
+      <x:c r="E9" s="185"/>
+      <x:c r="F9" s="185"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="176" t="str">
+        <x:v>2026-09-02现价</x:v>
+      </x:c>
+      <x:c r="B10" s="185" t="n">
+        <x:v>66.42</x:v>
+      </x:c>
+      <x:c r="C10" s="185" t="n">
+        <x:v>66.42</x:v>
+      </x:c>
+      <x:c r="D10" s="185" t="n">
+        <x:v>66.42</x:v>
+      </x:c>
+      <x:c r="E10" s="185" t="n">
+        <x:v>66.42</x:v>
+      </x:c>
+      <x:c r="F10" s="185" t="n">
+        <x:v>66.42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="176" t="str">
+        <x:v>2026E</x:v>
+      </x:c>
+      <x:c r="B11" s="185"/>
+      <x:c r="C11" s="185" t="n">
+        <x:f>'更新后预测'!M5</x:f>
+        <x:v>8.8</x:v>
+      </x:c>
+      <x:c r="D11" s="185" t="n">
+        <x:f>'更新后预测'!M10</x:f>
+        <x:v>18.5</x:v>
+      </x:c>
+      <x:c r="E11" s="185" t="n">
+        <x:f>'更新后预测'!M15</x:f>
+        <x:v>23.3</x:v>
+      </x:c>
+      <x:c r="F11" s="185" t="n">
+        <x:f>'更新后预测'!M20</x:f>
+        <x:v>88.82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="176" t="str">
+        <x:v>2027E</x:v>
+      </x:c>
+      <x:c r="B12" s="185"/>
+      <x:c r="C12" s="185" t="n">
+        <x:f>'更新后预测'!M6</x:f>
+        <x:v>6.5</x:v>
+      </x:c>
+      <x:c r="D12" s="185" t="n">
+        <x:f>'更新后预测'!M11</x:f>
+        <x:v>19.2</x:v>
+      </x:c>
+      <x:c r="E12" s="185" t="n">
+        <x:f>'更新后预测'!M16</x:f>
+        <x:v>25.3</x:v>
+      </x:c>
+      <x:c r="F12" s="185" t="n">
+        <x:f>'更新后预测'!M21</x:f>
+        <x:v>60.599</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="176" t="str">
+        <x:v>2028E</x:v>
+      </x:c>
+      <x:c r="B13" s="185"/>
+      <x:c r="C13" s="185" t="n">
+        <x:f>'更新后预测'!M7</x:f>
+        <x:v>5.7</x:v>
+      </x:c>
+      <x:c r="D13" s="185" t="n">
+        <x:f>'更新后预测'!M12</x:f>
+        <x:v>20.2</x:v>
+      </x:c>
+      <x:c r="E13" s="185" t="n">
+        <x:f>'更新后预测'!M17</x:f>
+        <x:v>26.5</x:v>
+      </x:c>
+      <x:c r="F13" s="185" t="n">
+        <x:f>'更新后预测'!M22</x:f>
+        <x:v>50.723</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="176" t="str">
+        <x:v>2029E</x:v>
+      </x:c>
+      <x:c r="B14" s="185"/>
+      <x:c r="C14" s="185" t="n">
+        <x:f>'更新后预测'!M8</x:f>
+        <x:v>5.4</x:v>
+      </x:c>
+      <x:c r="D14" s="185" t="n">
+        <x:f>'更新后预测'!M13</x:f>
+        <x:v>21.1</x:v>
+      </x:c>
+      <x:c r="E14" s="185" t="n">
+        <x:f>'更新后预测'!M18</x:f>
+        <x:v>26.8</x:v>
+      </x:c>
+      <x:c r="F14" s="185" t="n">
+        <x:f>'更新后预测'!M23</x:f>
+        <x:v>47.255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="176" t="str">
+        <x:v>2030E</x:v>
+      </x:c>
+      <x:c r="B15" s="185"/>
+      <x:c r="C15" s="185" t="n">
+        <x:f>'更新后预测'!M9</x:f>
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="D15" s="185" t="n">
+        <x:f>'更新后预测'!M14</x:f>
+        <x:v>21.6</x:v>
+      </x:c>
+      <x:c r="E15" s="185" t="n">
+        <x:f>'更新后预测'!M19</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F15" s="185" t="n">
+        <x:f>'更新后预测'!M24</x:f>
+        <x:v>40.963</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="174" t="str">
+        <x:v>期间</x:v>
+      </x:c>
+      <x:c r="B19" s="174" t="str">
+        <x:v>历史收盘价</x:v>
+      </x:c>
+      <x:c r="C19" s="174" t="str">
+        <x:v>Bear合理价</x:v>
+      </x:c>
+      <x:c r="D19" s="174" t="str">
+        <x:v>Base合理价</x:v>
+      </x:c>
+      <x:c r="E19" s="174" t="str">
+        <x:v>Bull合理价</x:v>
+      </x:c>
+      <x:c r="F19" s="174" t="str">
+        <x:v>Super Bull合理价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="176" t="str">
+        <x:v>2021A</x:v>
+      </x:c>
+      <x:c r="B20" s="185" t="n">
+        <x:v>0.78</x:v>
+      </x:c>
+      <x:c r="C20" s="185"/>
+      <x:c r="D20" s="185"/>
+      <x:c r="E20" s="185"/>
+      <x:c r="F20" s="185"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="176" t="str">
+        <x:v>2022A</x:v>
+      </x:c>
+      <x:c r="B21" s="185" t="n">
+        <x:v>0.81</x:v>
+      </x:c>
+      <x:c r="C21" s="185"/>
+      <x:c r="D21" s="185"/>
+      <x:c r="E21" s="185"/>
+      <x:c r="F21" s="185"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="176" t="str">
+        <x:v>2023A</x:v>
+      </x:c>
+      <x:c r="B22" s="185" t="n">
+        <x:v>1.72</x:v>
+      </x:c>
+      <x:c r="C22" s="185"/>
+      <x:c r="D22" s="185"/>
+      <x:c r="E22" s="185"/>
+      <x:c r="F22" s="185"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="176" t="str">
+        <x:v>2024A</x:v>
+      </x:c>
+      <x:c r="B23" s="185" t="n">
+        <x:v>1.66</x:v>
+      </x:c>
+      <x:c r="C23" s="185"/>
+      <x:c r="D23" s="185"/>
+      <x:c r="E23" s="185"/>
+      <x:c r="F23" s="185"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="176" t="str">
+        <x:v>2025A</x:v>
+      </x:c>
+      <x:c r="B24" s="185" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="C24" s="185"/>
+      <x:c r="D24" s="185"/>
+      <x:c r="E24" s="185"/>
+      <x:c r="F24" s="185"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="176" t="str">
+        <x:v>2026-09-02现价</x:v>
+      </x:c>
+      <x:c r="B25" s="185" t="n">
+        <x:v>2.43</x:v>
+      </x:c>
+      <x:c r="C25" s="185" t="n">
+        <x:v>2.43</x:v>
+      </x:c>
+      <x:c r="D25" s="185" t="n">
+        <x:v>2.43</x:v>
+      </x:c>
+      <x:c r="E25" s="185" t="n">
+        <x:v>2.43</x:v>
+      </x:c>
+      <x:c r="F25" s="185" t="n">
+        <x:v>2.43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="176" t="str">
+        <x:v>2026E</x:v>
+      </x:c>
+      <x:c r="B26" s="185"/>
+      <x:c r="C26" s="185" t="n">
+        <x:f>'更新后预测'!M25</x:f>
+        <x:v>0.49598796540984463</x:v>
+      </x:c>
+      <x:c r="D26" s="185" t="n">
+        <x:f>'更新后预测'!M30</x:f>
+        <x:v>0.8806173328827545</x:v>
+      </x:c>
+      <x:c r="E26" s="185" t="n">
+        <x:f>'更新后预测'!M35</x:f>
+        <x:v>1.3220806437512311</x:v>
+      </x:c>
+      <x:c r="F26" s="185" t="n">
+        <x:f>'更新后预测'!M40</x:f>
+        <x:v>6.228191826185085</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="176" t="str">
+        <x:v>2027E</x:v>
+      </x:c>
+      <x:c r="B27" s="185"/>
+      <x:c r="C27" s="185" t="n">
+        <x:f>'更新后预测'!M26</x:f>
+        <x:v>0.5653207423239497</x:v>
+      </x:c>
+      <x:c r="D27" s="185" t="n">
+        <x:f>'更新后预测'!M31</x:f>
+        <x:v>0.9655179820514446</x:v>
+      </x:c>
+      <x:c r="E27" s="185" t="n">
+        <x:f>'更新后预测'!M36</x:f>
+        <x:v>1.397697556223208</x:v>
+      </x:c>
+      <x:c r="F27" s="185" t="n">
+        <x:f>'更新后预测'!M41</x:f>
+        <x:v>5.2447916007371695</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="176" t="str">
+        <x:v>2028E</x:v>
+      </x:c>
+      <x:c r="B28" s="185"/>
+      <x:c r="C28" s="185" t="n">
+        <x:f>'更新后预测'!M27</x:f>
+        <x:v>0.5488427386971126</x:v>
+      </x:c>
+      <x:c r="D28" s="185" t="n">
+        <x:f>'更新后预测'!M32</x:f>
+        <x:v>0.9099178957398136</x:v>
+      </x:c>
+      <x:c r="E28" s="185" t="n">
+        <x:f>'更新后预测'!M37</x:f>
+        <x:v>1.330280115559939</x:v>
+      </x:c>
+      <x:c r="F28" s="185" t="n">
+        <x:f>'更新后预测'!M42</x:f>
+        <x:v>3.933593471482481</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="176" t="str">
+        <x:v>2029E</x:v>
+      </x:c>
+      <x:c r="B29" s="185"/>
+      <x:c r="C29" s="185" t="n">
+        <x:f>'更新后预测'!M28</x:f>
+        <x:v>0.5191953969630418</x:v>
+      </x:c>
+      <x:c r="D29" s="185" t="n">
+        <x:f>'更新后预测'!M33</x:f>
+        <x:v>0.8908151121420596</x:v>
+      </x:c>
+      <x:c r="E29" s="185" t="n">
+        <x:f>'更新后预测'!M38</x:f>
+        <x:v>1.2857568345426678</x:v>
+      </x:c>
+      <x:c r="F29" s="185" t="n">
+        <x:f>'更新后预测'!M43</x:f>
+        <x:v>4.678691322487034</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="176" t="str">
+        <x:v>2030E</x:v>
+      </x:c>
+      <x:c r="B30" s="185"/>
+      <x:c r="C30" s="185" t="n">
+        <x:f>'更新后预测'!M29</x:f>
+        <x:v>0.44565240234284165</x:v>
+      </x:c>
+      <x:c r="D30" s="185" t="n">
+        <x:f>'更新后预测'!M34</x:f>
+        <x:v>0.8742132692656102</x:v>
+      </x:c>
+      <x:c r="E30" s="185" t="n">
+        <x:f>'更新后预测'!M39</x:f>
+        <x:v>1.2713682236537283</x:v>
+      </x:c>
+      <x:c r="F30" s="185" t="n">
+        <x:f>'更新后预测'!M44</x:f>
+        <x:v>4.7364167805291855</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="174" t="str">
+        <x:v>期间</x:v>
+      </x:c>
+      <x:c r="B34" s="174" t="str">
+        <x:v>历史收盘价</x:v>
+      </x:c>
+      <x:c r="C34" s="174" t="str">
+        <x:v>Bear合理价</x:v>
+      </x:c>
+      <x:c r="D34" s="174" t="str">
+        <x:v>Base合理价</x:v>
+      </x:c>
+      <x:c r="E34" s="174" t="str">
+        <x:v>Bull合理价</x:v>
+      </x:c>
+      <x:c r="F34" s="174" t="str">
+        <x:v>Super Bull合理价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="176" t="str">
+        <x:v>2021A</x:v>
+      </x:c>
+      <x:c r="B35" s="185" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="C35" s="185"/>
+      <x:c r="D35" s="185"/>
+      <x:c r="E35" s="185"/>
+      <x:c r="F35" s="185"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="176" t="str">
+        <x:v>2022A</x:v>
+      </x:c>
+      <x:c r="B36" s="185" t="n">
+        <x:v>2.06</x:v>
+      </x:c>
+      <x:c r="C36" s="185"/>
+      <x:c r="D36" s="185"/>
+      <x:c r="E36" s="185"/>
+      <x:c r="F36" s="185"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="176" t="str">
+        <x:v>2023A</x:v>
+      </x:c>
+      <x:c r="B37" s="185" t="n">
+        <x:v>1.69</x:v>
+      </x:c>
+      <x:c r="C37" s="185"/>
+      <x:c r="D37" s="185"/>
+      <x:c r="E37" s="185"/>
+      <x:c r="F37" s="185"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="176" t="str">
+        <x:v>2024A</x:v>
+      </x:c>
+      <x:c r="B38" s="185" t="n">
+        <x:v>1.68</x:v>
+      </x:c>
+      <x:c r="C38" s="185"/>
+      <x:c r="D38" s="185"/>
+      <x:c r="E38" s="185"/>
+      <x:c r="F38" s="185"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="176" t="str">
+        <x:v>2025A</x:v>
+      </x:c>
+      <x:c r="B39" s="185" t="n">
+        <x:v>4.76</x:v>
+      </x:c>
+      <x:c r="C39" s="185"/>
+      <x:c r="D39" s="185"/>
+      <x:c r="E39" s="185"/>
+      <x:c r="F39" s="185"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="176" t="str">
+        <x:v>2026-09-02现价</x:v>
+      </x:c>
+      <x:c r="B40" s="185" t="n">
+        <x:v>3.85</x:v>
+      </x:c>
+      <x:c r="C40" s="185" t="n">
+        <x:v>3.85</x:v>
+      </x:c>
+      <x:c r="D40" s="185" t="n">
+        <x:v>3.85</x:v>
+      </x:c>
+      <x:c r="E40" s="185" t="n">
+        <x:v>3.85</x:v>
+      </x:c>
+      <x:c r="F40" s="185" t="n">
+        <x:v>3.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="176" t="str">
+        <x:v>2026E</x:v>
+      </x:c>
+      <x:c r="B41" s="185"/>
+      <x:c r="C41" s="185" t="n">
+        <x:f>'更新后预测'!M45</x:f>
+        <x:v>1.5906286774408125</x:v>
+      </x:c>
+      <x:c r="D41" s="185" t="n">
+        <x:f>'更新后预测'!M50</x:f>
+        <x:v>2.671886032322437</x:v>
+      </x:c>
+      <x:c r="E41" s="185" t="n">
+        <x:f>'更新后预测'!M55</x:f>
+        <x:v>3.5396004947237913</x:v>
+      </x:c>
+      <x:c r="F41" s="185" t="n">
+        <x:f>'更新后预测'!M60</x:f>
+        <x:v>3.5762553284625302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="176" t="str">
+        <x:v>2027E</x:v>
+      </x:c>
+      <x:c r="B42" s="185"/>
+      <x:c r="C42" s="185" t="n">
+        <x:f>'更新后预测'!M46</x:f>
+        <x:v>1.7859430161612186</x:v>
+      </x:c>
+      <x:c r="D42" s="185" t="n">
+        <x:f>'更新后预测'!M51</x:f>
+        <x:v>3.5896004947237916</x:v>
+      </x:c>
+      <x:c r="E42" s="185" t="n">
+        <x:f>'更新后预测'!M56</x:f>
+        <x:v>4.684400742085687</x:v>
+      </x:c>
+      <x:c r="F42" s="185" t="n">
+        <x:f>'更新后预测'!M61</x:f>
+        <x:v>2.6821914963468974</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="176" t="str">
+        <x:v>2028E</x:v>
+      </x:c>
+      <x:c r="B43" s="185"/>
+      <x:c r="C43" s="185" t="n">
+        <x:f>'更新后预测'!M47</x:f>
+        <x:v>1.8586001855214218</x:v>
+      </x:c>
+      <x:c r="D43" s="185" t="n">
+        <x:f>'更新后预测'!M52</x:f>
+        <x:v>4.312000618404739</x:v>
+      </x:c>
+      <x:c r="E43" s="185" t="n">
+        <x:f>'更新后预测'!M57</x:f>
+        <x:v>5.779200989447583</x:v>
+      </x:c>
+      <x:c r="F43" s="185" t="n">
+        <x:f>'更新后预测'!M62</x:f>
+        <x:v>2.38417021897502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="176" t="str">
+        <x:v>2029E</x:v>
+      </x:c>
+      <x:c r="B44" s="185"/>
+      <x:c r="C44" s="185" t="n">
+        <x:f>'更新后预测'!M48</x:f>
+        <x:v>1.8699287702015233</x:v>
+      </x:c>
+      <x:c r="D44" s="185" t="n">
+        <x:f>'更新后预测'!M53</x:f>
+        <x:v>4.952629295845552</x:v>
+      </x:c>
+      <x:c r="E44" s="185" t="n">
+        <x:f>'更新后预测'!M58</x:f>
+        <x:v>6.546915451848937</x:v>
+      </x:c>
+      <x:c r="F44" s="185" t="n">
+        <x:f>'更新后预测'!M63</x:f>
+        <x:v>7.241816612126066</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="176" t="str">
+        <x:v>2030E</x:v>
+      </x:c>
+      <x:c r="B45" s="185"/>
+      <x:c r="C45" s="185" t="n">
+        <x:f>'更新后预测'!M49</x:f>
+        <x:v>1.881257354881625</x:v>
+      </x:c>
+      <x:c r="D45" s="185" t="n">
+        <x:f>'更新后预测'!M54</x:f>
+        <x:v>5.429715080806093</x:v>
+      </x:c>
+      <x:c r="E45" s="185" t="n">
+        <x:f>'更新后预测'!M59</x:f>
+        <x:v>7.069315575529885</x:v>
+      </x:c>
+      <x:c r="F45" s="185" t="n">
+        <x:f>'更新后预测'!M64</x:f>
+        <x:v>13.185645706221834</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:P1"/>
+    <x:mergeCell ref="A2:P2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bb6bb0cf7b343fe"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="165" t="str">
+        <x:v>模型更新记录</x:v>
+      </x:c>
+      <x:c r="B1" s="165"/>
+      <x:c r="C1" s="165"/>
+      <x:c r="D1" s="165"/>
+      <x:c r="E1" s="165"/>
+      <x:c r="F1" s="165"/>
+      <x:c r="G1" s="165"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="169" t="str">
+        <x:v>保留旧表和旧假设作为审计轨迹；新增表是2026-09-02版本。所有结论变化均可追溯至最新中报或市场价格锚点。</x:v>
+      </x:c>
+      <x:c r="B2" s="169"/>
+      <x:c r="C2" s="169"/>
+      <x:c r="D2" s="169"/>
+      <x:c r="E2" s="169"/>
+      <x:c r="F2" s="169"/>
+      <x:c r="G2" s="169"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="174" t="str">
+        <x:v>版本</x:v>
+      </x:c>
+      <x:c r="B4" s="174" t="str">
+        <x:v>对象</x:v>
+      </x:c>
+      <x:c r="C4" s="174" t="str">
+        <x:v>更新项</x:v>
+      </x:c>
+      <x:c r="D4" s="174" t="str">
+        <x:v>旧口径</x:v>
+      </x:c>
+      <x:c r="E4" s="174" t="str">
+        <x:v>新口径</x:v>
+      </x:c>
+      <x:c r="F4" s="174" t="str">
+        <x:v>影响</x:v>
+      </x:c>
+      <x:c r="G4" s="174" t="str">
+        <x:v>原因/来源</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="181" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="B5" s="181" t="str">
+        <x:v>中国铀业</x:v>
+      </x:c>
+      <x:c r="C5" s="181" t="str">
+        <x:v>2026H1经营数据</x:v>
+      </x:c>
+      <x:c r="D5" s="181" t="str">
+        <x:v>仅2026Q1和旧情景</x:v>
+      </x:c>
+      <x:c r="E5" s="181" t="str">
+        <x:v>收入10582.9、归母987.4、CFO349.0；应收5507.2</x:v>
+      </x:c>
+      <x:c r="F5" s="181" t="str">
+        <x:v>近端盈利可信度上升；现金流风险转向应收回款</x:v>
+      </x:c>
+      <x:c r="G5" s="181" t="str">
+        <x:v>2026H1官方中报</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="181" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="B6" s="181" t="str">
+        <x:v>中广核矿业</x:v>
+      </x:c>
+      <x:c r="C6" s="181" t="str">
+        <x:v>利润与成本</x:v>
+      </x:c>
+      <x:c r="D6" s="181" t="str">
+        <x:v>旧模型未纳入H1硫酸成本冲击</x:v>
+      </x:c>
+      <x:c r="E6" s="181" t="str">
+        <x:v>下调2026—2030净利润；标准SOTP再施加10%成本折价</x:v>
+      </x:c>
+      <x:c r="F6" s="181" t="str">
+        <x:v>Base 2030合理价约1.01降至0.87港元</x:v>
+      </x:c>
+      <x:c r="G6" s="181" t="str">
+        <x:v>2026H1官方中报</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="181" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="B7" s="181" t="str">
+        <x:v>中核国际</x:v>
+      </x:c>
+      <x:c r="C7" s="181" t="str">
+        <x:v>交易量与现金</x:v>
+      </x:c>
+      <x:c r="D7" s="181" t="str">
+        <x:v>Base 2026收入2435、2030净利272</x:v>
+      </x:c>
+      <x:c r="E7" s="181" t="str">
+        <x:v>Base 2026收入1500、2030净利225；更新净现金路径</x:v>
+      </x:c>
+      <x:c r="F7" s="181" t="str">
+        <x:v>Base 2030合理价5.88降至约5.43港元</x:v>
+      </x:c>
+      <x:c r="G7" s="181" t="str">
+        <x:v>2026H1官方中报</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="181" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="B8" s="181" t="str">
+        <x:v>三家公司</x:v>
+      </x:c>
+      <x:c r="C8" s="181" t="str">
+        <x:v>当前价</x:v>
+      </x:c>
+      <x:c r="D8" s="181" t="str">
+        <x:v>2026-08-21收盘价</x:v>
+      </x:c>
+      <x:c r="E8" s="181" t="str">
+        <x:v>2026-09-02未复权收盘价</x:v>
+      </x:c>
+      <x:c r="F8" s="181" t="str">
+        <x:v>TSR和最大买价统一重算</x:v>
+      </x:c>
+      <x:c r="G8" s="181" t="str">
+        <x:v>Yahoo Finance历史行情</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="181" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="B9" s="181" t="str">
+        <x:v>三家公司</x:v>
+      </x:c>
+      <x:c r="C9" s="181" t="str">
+        <x:v>股价图口径</x:v>
+      </x:c>
+      <x:c r="D9" s="181" t="str">
+        <x:v>仅表格展示2030价值</x:v>
+      </x:c>
+      <x:c r="E9" s="181" t="str">
+        <x:v>历史年末未复权收盘价+2026-09-02现价+2026E—2030E年末合理价</x:v>
+      </x:c>
+      <x:c r="F9" s="181" t="str">
+        <x:v>可以直接看当前价格与各情景收敛关系</x:v>
+      </x:c>
+      <x:c r="G9" s="181" t="str">
+        <x:v>新增原生Excel图表与文章ECharts</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A2:G2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="40" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="165" t="str">
+        <x:v>2026H1 更新检查</x:v>
+      </x:c>
+      <x:c r="B1" s="165"/>
+      <x:c r="C1" s="165"/>
+      <x:c r="D1" s="165"/>
+      <x:c r="E1" s="165"/>
+      <x:c r="F1" s="165"/>
+      <x:c r="G1" s="165"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="169" t="str">
+        <x:v>Actual、Diff和Status均由公式计算；全部为OK后方可交付。容差用于处理公式浮点误差。</x:v>
+      </x:c>
+      <x:c r="B2" s="169"/>
+      <x:c r="C2" s="169"/>
+      <x:c r="D2" s="169"/>
+      <x:c r="E2" s="169"/>
+      <x:c r="F2" s="169"/>
+      <x:c r="G2" s="169"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="174" t="str">
+        <x:v>检查项</x:v>
+      </x:c>
+      <x:c r="B4" s="174" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="C4" s="174" t="str">
+        <x:v>Expected</x:v>
+      </x:c>
+      <x:c r="D4" s="174" t="str">
+        <x:v>Diff</x:v>
+      </x:c>
+      <x:c r="E4" s="174" t="str">
+        <x:v>Tolerance</x:v>
+      </x:c>
+      <x:c r="F4" s="174" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G4" s="174" t="str">
+        <x:v>说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="176" t="str">
+        <x:v>预测行数</x:v>
+      </x:c>
+      <x:c r="B5" s="176" t="n">
+        <x:f>COUNTA('更新后预测'!A5:A64)</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C5" s="176" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D5" s="176" t="n">
+        <x:f>B5-C5</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" s="176" t="str">
+        <x:f>IF(ABS(D5)&lt;=E5,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G5" s="176" t="str">
+        <x:v>3家公司×4情景×5年</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="176" t="str">
+        <x:v>估值行数</x:v>
+      </x:c>
+      <x:c r="B6" s="176" t="n">
+        <x:f>COUNTA('更新后估值'!A5:A16)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C6" s="176" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D6" s="176" t="n">
+        <x:f>B6-C6</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="176" t="str">
+        <x:f>IF(ABS(D6)&lt;=E6,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G6" s="176" t="str">
+        <x:v>3家公司×4情景</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="176" t="str">
+        <x:v>通过11%情景数</x:v>
+      </x:c>
+      <x:c r="B7" s="176" t="n">
+        <x:f>COUNTIF('更新后估值'!J5:J16,"通过")</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="176" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="176" t="n">
+        <x:f>B7-C7</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="176" t="str">
+        <x:f>IF(ABS(D7)&lt;=E7,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G7" s="176" t="str">
+        <x:v>中广核SB；中核国际Bull/SB</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="176" t="str">
+        <x:v>中国铀业Base 2030合理价</x:v>
+      </x:c>
+      <x:c r="B8" s="176" t="n">
+        <x:f>'更新后预测'!M14</x:f>
+        <x:v>21.6</x:v>
+      </x:c>
+      <x:c r="C8" s="176" t="n">
+        <x:v>21.6</x:v>
+      </x:c>
+      <x:c r="D8" s="176" t="n">
+        <x:f>B8-C8</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="176" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F8" s="176" t="str">
+        <x:f>IF(ABS(D8)&lt;=E8,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G8" s="176" t="str">
+        <x:v>SOTP输入与输出连接</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="176" t="str">
+        <x:v>中广核Base 2030合理价</x:v>
+      </x:c>
+      <x:c r="B9" s="176" t="n">
+        <x:f>'更新后预测'!M34</x:f>
+        <x:v>0.8742132692656102</x:v>
+      </x:c>
+      <x:c r="C9" s="176" t="n">
+        <x:v>0.8742132692656102</x:v>
+      </x:c>
+      <x:c r="D9" s="176" t="n">
+        <x:f>B9-C9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="176" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F9" s="176" t="str">
+        <x:f>IF(ABS(D9)&lt;=E9,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G9" s="176" t="str">
+        <x:v>旧SOTP×成本折价×利润修正</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="176" t="str">
+        <x:v>中核国际Base 2030合理价</x:v>
+      </x:c>
+      <x:c r="B10" s="176" t="n">
+        <x:f>'更新后预测'!M54</x:f>
+        <x:v>5.429715080806093</x:v>
+      </x:c>
+      <x:c r="C10" s="176" t="n">
+        <x:v>5.429715080806093</x:v>
+      </x:c>
+      <x:c r="D10" s="176" t="n">
+        <x:f>B10-C10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="176" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F10" s="176" t="str">
+        <x:f>IF(ABS(D10)&lt;=E10,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G10" s="176" t="str">
+        <x:v>PE+净现金</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="176" t="str">
+        <x:v>中国铀业现价</x:v>
+      </x:c>
+      <x:c r="B11" s="176" t="n">
+        <x:f>'更新后估值'!C5</x:f>
+        <x:v>66.42</x:v>
+      </x:c>
+      <x:c r="C11" s="176" t="n">
+        <x:v>66.42</x:v>
+      </x:c>
+      <x:c r="D11" s="176" t="n">
+        <x:f>B11-C11</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="176" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F11" s="176" t="str">
+        <x:f>IF(ABS(D11)&lt;=E11,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G11" s="176" t="str">
+        <x:v>2026-09-02收盘</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="176" t="str">
+        <x:v>中广核矿业现价</x:v>
+      </x:c>
+      <x:c r="B12" s="176" t="n">
+        <x:f>'更新后估值'!C9</x:f>
+        <x:v>2.43</x:v>
+      </x:c>
+      <x:c r="C12" s="176" t="n">
+        <x:v>2.43</x:v>
+      </x:c>
+      <x:c r="D12" s="176" t="n">
+        <x:f>B12-C12</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="176" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F12" s="176" t="str">
+        <x:f>IF(ABS(D12)&lt;=E12,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G12" s="176" t="str">
+        <x:v>2026-09-02收盘</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="176" t="str">
+        <x:v>中核国际现价</x:v>
+      </x:c>
+      <x:c r="B13" s="176" t="n">
+        <x:f>'更新后估值'!C13</x:f>
+        <x:v>3.85</x:v>
+      </x:c>
+      <x:c r="C13" s="176" t="n">
+        <x:v>3.85</x:v>
+      </x:c>
+      <x:c r="D13" s="176" t="n">
+        <x:f>B13-C13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="176" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F13" s="176" t="str">
+        <x:f>IF(ABS(D13)&lt;=E13,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G13" s="176" t="str">
+        <x:v>2026-09-02收盘</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="176" t="str">
+        <x:v>合理价全部为正</x:v>
+      </x:c>
+      <x:c r="B14" s="176" t="n">
+        <x:f>MIN('更新后预测'!M5:M64)</x:f>
+        <x:v>0.44565240234284165</x:v>
+      </x:c>
+      <x:c r="C14" s="176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="176" t="n">
+        <x:f>B14-C14</x:f>
+        <x:v>0.44565240234284165</x:v>
+      </x:c>
+      <x:c r="E14" s="176" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="176" t="str">
+        <x:f>IF(B14&gt;0,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G14" s="176" t="str">
+        <x:v>防止公式断链或负值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="176"/>
+      <x:c r="B15" s="176"/>
+      <x:c r="C15" s="176"/>
+      <x:c r="D15" s="176"/>
+      <x:c r="E15" s="176"/>
+      <x:c r="F15" s="176"/>
+      <x:c r="G15" s="176"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="176" t="str">
+        <x:v>总体状态</x:v>
+      </x:c>
+      <x:c r="B16" s="176"/>
+      <x:c r="C16" s="176"/>
+      <x:c r="D16" s="176"/>
+      <x:c r="E16" s="176"/>
+      <x:c r="F16" s="176" t="str">
+        <x:f>IF(COUNTIF(F5:F14,"FAIL")=0,"OK","FAIL")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="G16" s="176" t="str">
+        <x:v>全部检查为OK才可交付</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A2:G2"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="F5:F16">
+    <x:cfRule type="expression" dxfId="4" priority="1">
+      <x:formula>F5="OK"</x:formula>
+    </x:cfRule>
+    <x:cfRule type="expression" dxfId="5" priority="2">
+      <x:formula>F5="FAIL"</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
